--- a/data/publications/monthly-rbi-bulletin/prices-and-production/table-21-monthly-average-price-of-gold-and-silver-in-mumbai.xlsx
+++ b/data/publications/monthly-rbi-bulletin/prices-and-production/table-21-monthly-average-price-of-gold-and-silver-in-mumbai.xlsx
@@ -224,11 +224,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D436"/>
+  <dimension ref="A1:E443"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="4" width="15.4582386666667" customWidth="1"/>
     <col min="5" max="5" width="15.454436" customWidth="1"/>
+    <col min="6" max="6" width="4.68148133333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -254,4747 +255,4814 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B5" s="4">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="C5" s="5">
-        <v>145946.9</v>
+        <v>142605.83</v>
       </c>
       <c r="D5" s="6">
-        <v>285592.95</v>
+        <v>222395.52</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B6" s="4">
-        <v>45992</v>
+        <v>46174</v>
       </c>
       <c r="C6" s="7">
-        <v>131171.5455</v>
+        <v>148095.48</v>
       </c>
       <c r="D6" s="8">
-        <v>198182.3182</v>
+        <v>241742.81</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B7" s="4">
-        <v>45962</v>
+        <v>46143</v>
       </c>
       <c r="C7" s="5">
-        <v>122961.8421</v>
+        <v>154756.37</v>
       </c>
       <c r="D7" s="6">
-        <v>155010.2105</v>
+        <v>263202.32</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B8" s="4">
-        <v>45931</v>
+        <v>46113</v>
       </c>
       <c r="C8" s="7">
-        <v>121907.67</v>
+        <v>149927.3</v>
       </c>
       <c r="D8" s="8">
-        <v>155904.48</v>
+        <v>241672.15</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B9" s="4">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="C9" s="5">
-        <v>109590.91</v>
+        <v>153298.84</v>
       </c>
       <c r="D9" s="6">
-        <v>129256.68</v>
+        <v>250290.79</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B10" s="4">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C10" s="7">
-        <v>99696.47</v>
+        <v>154038.5238</v>
       </c>
       <c r="D10" s="8">
-        <v>114031.95</v>
+        <v>256061.0952</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B11" s="4">
-        <v>45839</v>
+        <v>46023</v>
       </c>
       <c r="C11" s="5">
-        <v>97581.22</v>
+        <v>145946.9</v>
       </c>
       <c r="D11" s="6">
-        <v>110957.96</v>
+        <v>285592.95</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B12" s="4">
-        <v>45809</v>
+        <v>45992</v>
       </c>
       <c r="C12" s="7">
-        <v>97175.81</v>
+        <v>131171.5455</v>
       </c>
       <c r="D12" s="8">
-        <v>105444.43</v>
+        <v>198182.3182</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B13" s="4">
-        <v>45778</v>
+        <v>45962</v>
       </c>
       <c r="C13" s="5">
-        <v>94589.81</v>
+        <v>122961.8421</v>
       </c>
       <c r="D13" s="6">
-        <v>96025.62</v>
+        <v>155010.2105</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B14" s="4">
-        <v>45748</v>
+        <v>45931</v>
       </c>
       <c r="C14" s="7">
-        <v>93091.21</v>
+        <v>121907.67</v>
       </c>
       <c r="D14" s="8">
-        <v>95308.58</v>
+        <v>155904.48</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B15" s="4">
-        <v>45717</v>
+        <v>45901</v>
       </c>
       <c r="C15" s="5">
-        <v>86890.11</v>
+        <v>109590.91</v>
       </c>
       <c r="D15" s="6">
-        <v>97867.74</v>
+        <v>129256.68</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B16" s="4">
-        <v>45689</v>
+        <v>45870</v>
       </c>
       <c r="C16" s="7">
-        <v>84995.47</v>
+        <v>99696.47</v>
       </c>
       <c r="D16" s="8">
-        <v>95524.26</v>
+        <v>114031.95</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B17" s="4">
-        <v>45658</v>
+        <v>45839</v>
       </c>
       <c r="C17" s="5">
-        <v>79079</v>
+        <v>97581.22</v>
       </c>
       <c r="D17" s="6">
-        <v>90020.43</v>
+        <v>110957.96</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B18" s="4">
-        <v>45627</v>
+        <v>45809</v>
       </c>
       <c r="C18" s="7">
-        <v>76195.05</v>
+        <v>97175.81</v>
       </c>
       <c r="D18" s="8">
-        <v>89264.86</v>
+        <v>105444.43</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B19" s="4">
-        <v>45597</v>
+        <v>45778</v>
       </c>
       <c r="C19" s="5">
-        <v>76220.94444</v>
+        <v>94589.81</v>
       </c>
       <c r="D19" s="6">
-        <v>90230.05556</v>
+        <v>96025.62</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B20" s="4">
-        <v>45566</v>
+        <v>45748</v>
       </c>
       <c r="C20" s="7">
-        <v>76713.09091</v>
+        <v>93091.21</v>
       </c>
       <c r="D20" s="8">
-        <v>93352.40909</v>
+        <v>95308.58</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B21" s="4">
-        <v>45536</v>
+        <v>45717</v>
       </c>
       <c r="C21" s="5">
-        <v>72877.62</v>
+        <v>86890.11</v>
       </c>
       <c r="D21" s="6">
-        <v>86187.43</v>
+        <v>97867.74</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B22" s="4">
-        <v>45505</v>
+        <v>45689</v>
       </c>
       <c r="C22" s="7">
-        <v>70440.71</v>
+        <v>84995.47</v>
       </c>
       <c r="D22" s="8">
-        <v>82750.71</v>
+        <v>95524.26</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B23" s="4">
-        <v>45474</v>
+        <v>45658</v>
       </c>
       <c r="C23" s="5">
-        <v>71188.55</v>
+        <v>79079</v>
       </c>
       <c r="D23" s="6">
-        <v>88057.77</v>
+        <v>90020.43</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B24" s="4">
-        <v>45444</v>
+        <v>45627</v>
       </c>
       <c r="C24" s="7">
-        <v>72014</v>
+        <v>76195.05</v>
       </c>
       <c r="D24" s="8">
-        <v>88666.26316</v>
+        <v>89264.86</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B25" s="4">
-        <v>45413</v>
+        <v>45597</v>
       </c>
       <c r="C25" s="5">
-        <v>72134.95</v>
+        <v>76220.94444</v>
       </c>
       <c r="D25" s="6">
-        <v>86866.14286</v>
+        <v>90230.05556</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B26" s="4">
-        <v>45383</v>
+        <v>45566</v>
       </c>
       <c r="C26" s="7">
-        <v>71353</v>
+        <v>76713.09091</v>
       </c>
       <c r="D26" s="8">
-        <v>80778.3</v>
+        <v>93352.40909</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B27" s="4">
-        <v>45352</v>
+        <v>45536</v>
       </c>
       <c r="C27" s="5">
-        <v>65229</v>
+        <v>72877.62</v>
       </c>
       <c r="D27" s="6">
-        <v>73109</v>
+        <v>86187.43</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B28" s="4">
-        <v>45323</v>
+        <v>45505</v>
       </c>
       <c r="C28" s="7">
-        <v>62017.33</v>
+        <v>70440.71</v>
       </c>
       <c r="D28" s="8">
-        <v>70327.66667</v>
+        <v>82750.71</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B29" s="4">
-        <v>45292</v>
+        <v>45474</v>
       </c>
       <c r="C29" s="5">
-        <v>62322.43</v>
+        <v>71188.55</v>
       </c>
       <c r="D29" s="6">
-        <v>71722.80952</v>
+        <v>88057.77</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B30" s="4">
-        <v>45261</v>
+        <v>45444</v>
       </c>
       <c r="C30" s="7">
-        <v>62172.95</v>
+        <v>72014</v>
       </c>
       <c r="D30" s="8">
-        <v>73925.65</v>
+        <v>88666.26316</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B31" s="4">
-        <v>45231</v>
+        <v>45413</v>
       </c>
       <c r="C31" s="5">
-        <v>60785.95</v>
+        <v>72134.95</v>
       </c>
       <c r="D31" s="6">
-        <v>72222.28571</v>
+        <v>86866.14286</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B32" s="4">
-        <v>45200</v>
+        <v>45383</v>
       </c>
       <c r="C32" s="7">
-        <v>58773.2</v>
+        <v>71353</v>
       </c>
       <c r="D32" s="8">
-        <v>70083.95</v>
+        <v>80778.3</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B33" s="4">
-        <v>45170</v>
+        <v>45352</v>
       </c>
       <c r="C33" s="5">
-        <v>58742.5</v>
+        <v>65229</v>
       </c>
       <c r="D33" s="6">
-        <v>71852.25</v>
+        <v>73109</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B34" s="4">
-        <v>45139</v>
+        <v>45323</v>
       </c>
       <c r="C34" s="7">
-        <v>58737.95</v>
+        <v>62017.33</v>
       </c>
       <c r="D34" s="8">
-        <v>72134.5</v>
+        <v>70327.66667</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B35" s="4">
-        <v>45108</v>
+        <v>45292</v>
       </c>
       <c r="C35" s="5">
-        <v>58921.71</v>
+        <v>62322.43</v>
       </c>
       <c r="D35" s="6">
-        <v>72944.66667</v>
+        <v>71722.80952</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B36" s="4">
-        <v>45078</v>
+        <v>45261</v>
       </c>
       <c r="C36" s="7">
-        <v>59056.38</v>
+        <v>62172.95</v>
       </c>
       <c r="D36" s="8">
-        <v>71190.29</v>
+        <v>73925.65</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B37" s="4">
-        <v>45047</v>
+        <v>45231</v>
       </c>
       <c r="C37" s="5">
-        <v>60582.77</v>
+        <v>60785.95</v>
       </c>
       <c r="D37" s="6">
-        <v>73014.5</v>
+        <v>72222.28571</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B38" s="4">
-        <v>45017</v>
+        <v>45200</v>
       </c>
       <c r="C38" s="7">
-        <v>60145.24</v>
+        <v>58773.2</v>
       </c>
       <c r="D38" s="8">
-        <v>74386.24</v>
+        <v>70083.95</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B39" s="4">
-        <v>44986</v>
+        <v>45170</v>
       </c>
       <c r="C39" s="5">
-        <v>57513.67</v>
+        <v>58742.5</v>
       </c>
       <c r="D39" s="6">
-        <v>66519.62</v>
+        <v>71852.25</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B40" s="4">
-        <v>44958</v>
+        <v>45139</v>
       </c>
       <c r="C40" s="7">
-        <v>56645.6</v>
+        <v>58737.95</v>
       </c>
       <c r="D40" s="8">
-        <v>66401.7</v>
+        <v>72134.5</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B41" s="4">
-        <v>44927</v>
+        <v>45108</v>
       </c>
       <c r="C41" s="5">
-        <v>56246.33</v>
+        <v>58921.71</v>
       </c>
       <c r="D41" s="6">
-        <v>68305.14</v>
+        <v>72944.66667</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B42" s="4">
-        <v>44896</v>
+        <v>45078</v>
       </c>
       <c r="C42" s="7">
-        <v>53940.82</v>
+        <v>59056.38</v>
       </c>
       <c r="D42" s="8">
-        <v>66698.45</v>
+        <v>71190.29</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B43" s="4">
-        <v>44866</v>
+        <v>45047</v>
       </c>
       <c r="C43" s="5">
-        <v>51873.62</v>
+        <v>60582.77</v>
       </c>
       <c r="D43" s="6">
-        <v>60968.14</v>
+        <v>73014.5</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B44" s="4">
-        <v>44835</v>
+        <v>45017</v>
       </c>
       <c r="C44" s="7">
-        <v>50506</v>
+        <v>60145.24</v>
       </c>
       <c r="D44" s="8">
-        <v>57505.32</v>
+        <v>74386.24</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B45" s="4">
-        <v>44805</v>
+        <v>44986</v>
       </c>
       <c r="C45" s="5">
-        <v>49913.55</v>
+        <v>57513.67</v>
       </c>
       <c r="D45" s="6">
-        <v>55231.95</v>
+        <v>66519.62</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B46" s="4">
-        <v>44774</v>
+        <v>44958</v>
       </c>
       <c r="C46" s="7">
-        <v>51639.15</v>
+        <v>56645.6</v>
       </c>
       <c r="D46" s="8">
-        <v>56831.3</v>
+        <v>66401.7</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B47" s="4">
-        <v>44743</v>
+        <v>44927</v>
       </c>
       <c r="C47" s="5">
-        <v>50784.33</v>
+        <v>56246.33</v>
       </c>
       <c r="D47" s="6">
-        <v>55994.33</v>
+        <v>68305.14</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B48" s="4">
-        <v>44713</v>
+        <v>44896</v>
       </c>
       <c r="C48" s="7">
-        <v>50804.23</v>
+        <v>53940.82</v>
       </c>
       <c r="D48" s="8">
-        <v>60936.36</v>
+        <v>66698.45</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B49" s="4">
-        <v>44682</v>
+        <v>44866</v>
       </c>
       <c r="C49" s="5">
-        <v>50879.43</v>
+        <v>51873.62</v>
       </c>
       <c r="D49" s="6">
-        <v>61572.43</v>
+        <v>60968.14</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B50" s="4">
-        <v>44652</v>
+        <v>44835</v>
       </c>
       <c r="C50" s="7">
-        <v>52022.53</v>
+        <v>50506</v>
       </c>
       <c r="D50" s="8">
-        <v>66922</v>
+        <v>57505.32</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B51" s="4">
-        <v>44621</v>
+        <v>44805</v>
       </c>
       <c r="C51" s="5">
-        <v>51750.29</v>
+        <v>49913.55</v>
       </c>
       <c r="D51" s="6">
-        <v>68285.62</v>
+        <v>55231.95</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B52" s="4">
-        <v>44593</v>
+        <v>44774</v>
       </c>
       <c r="C52" s="7">
-        <v>49254</v>
+        <v>51639.15</v>
       </c>
       <c r="D52" s="8">
-        <v>63174.6</v>
+        <v>56831.3</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B53" s="4">
-        <v>44562</v>
+        <v>44743</v>
       </c>
       <c r="C53" s="5">
-        <v>47960.25</v>
+        <v>50784.33</v>
       </c>
       <c r="D53" s="6">
-        <v>62037.85</v>
+        <v>55994.33</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B54" s="4">
-        <v>44531</v>
+        <v>44713</v>
       </c>
       <c r="C54" s="7">
-        <v>47889.83</v>
+        <v>50804.23</v>
       </c>
       <c r="D54" s="8">
-        <v>61280.43</v>
+        <v>60936.36</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B55" s="4">
-        <v>44501</v>
+        <v>44682</v>
       </c>
       <c r="C55" s="5">
-        <v>48192.85</v>
+        <v>50879.43</v>
       </c>
       <c r="D55" s="6">
-        <v>64667.15</v>
+        <v>61572.43</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B56" s="4">
-        <v>44470</v>
+        <v>44652</v>
       </c>
       <c r="C56" s="7">
-        <v>47218.79</v>
+        <v>52022.53</v>
       </c>
       <c r="D56" s="8">
-        <v>62890.42</v>
+        <v>66922</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B57" s="4">
-        <v>44440</v>
+        <v>44621</v>
       </c>
       <c r="C57" s="5">
-        <v>46584.14</v>
+        <v>51750.29</v>
       </c>
       <c r="D57" s="6">
-        <v>61892.29</v>
+        <v>68285.62</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B58" s="4">
-        <v>44409</v>
+        <v>44593</v>
       </c>
       <c r="C58" s="7">
-        <v>47108.95</v>
+        <v>49254</v>
       </c>
       <c r="D58" s="8">
-        <v>64219.48</v>
+        <v>63174.6</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B59" s="4">
-        <v>44378</v>
+        <v>44562</v>
       </c>
       <c r="C59" s="5">
-        <v>47763.52</v>
+        <v>47960.25</v>
       </c>
       <c r="D59" s="6">
-        <v>68338.19</v>
+        <v>62037.85</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B60" s="4">
-        <v>44348</v>
+        <v>44531</v>
       </c>
       <c r="C60" s="7">
-        <v>47890.86</v>
+        <v>47889.83</v>
       </c>
       <c r="D60" s="8">
-        <v>69959.95</v>
+        <v>61280.43</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B61" s="4">
-        <v>44317</v>
+        <v>44501</v>
       </c>
       <c r="C61" s="5">
-        <v>47860.25</v>
+        <v>48192.85</v>
       </c>
       <c r="D61" s="6">
-        <v>70833.35</v>
+        <v>64667.15</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B62" s="4">
-        <v>44287</v>
+        <v>44470</v>
       </c>
       <c r="C62" s="7">
-        <v>46517.21</v>
+        <v>47218.79</v>
       </c>
       <c r="D62" s="8">
-        <v>67528.42</v>
+        <v>62890.42</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B63" s="4">
-        <v>44256</v>
+        <v>44440</v>
       </c>
       <c r="C63" s="5">
-        <v>44648</v>
+        <v>46584.14</v>
       </c>
       <c r="D63" s="6">
-        <v>65981</v>
+        <v>61892.29</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B64" s="4">
-        <v>44228</v>
+        <v>44409</v>
       </c>
       <c r="C64" s="7">
-        <v>47107</v>
+        <v>47108.95</v>
       </c>
       <c r="D64" s="8">
-        <v>69065</v>
+        <v>64219.48</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B65" s="4">
-        <v>44197</v>
+        <v>44378</v>
       </c>
       <c r="C65" s="5">
-        <v>49612</v>
+        <v>47763.52</v>
       </c>
       <c r="D65" s="6">
-        <v>66785</v>
+        <v>68338.19</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B66" s="4">
-        <v>44166</v>
+        <v>44348</v>
       </c>
       <c r="C66" s="7">
-        <v>49443.86</v>
+        <v>47890.86</v>
       </c>
       <c r="D66" s="8">
-        <v>64756.5</v>
+        <v>69959.95</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B67" s="4">
-        <v>44136</v>
+        <v>44317</v>
       </c>
       <c r="C67" s="5">
-        <v>50428.65</v>
+        <v>47860.25</v>
       </c>
       <c r="D67" s="6">
-        <v>62255.55</v>
+        <v>70833.35</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B68" s="4">
-        <v>44105</v>
+        <v>44287</v>
       </c>
       <c r="C68" s="7">
-        <v>50697.85</v>
+        <v>46517.21</v>
       </c>
       <c r="D68" s="8">
-        <v>61319.9</v>
+        <v>67528.42</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B69" s="4">
-        <v>44075</v>
+        <v>44256</v>
       </c>
       <c r="C69" s="5">
-        <v>50783.64</v>
+        <v>44648</v>
       </c>
       <c r="D69" s="6">
-        <v>63337.05</v>
+        <v>65981</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B70" s="4">
-        <v>44044</v>
+        <v>44228</v>
       </c>
       <c r="C70" s="7">
-        <v>52917.19</v>
+        <v>47107</v>
       </c>
       <c r="D70" s="8">
-        <v>67717.48</v>
+        <v>69065</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B71" s="4">
-        <v>44013</v>
+        <v>44197</v>
       </c>
       <c r="C71" s="5">
-        <v>49878.43</v>
+        <v>49612</v>
       </c>
       <c r="D71" s="6">
-        <v>54813.48</v>
+        <v>66785</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B72" s="4">
-        <v>43983</v>
+        <v>44166</v>
       </c>
       <c r="C72" s="7">
-        <v>47314.73</v>
+        <v>49443.86</v>
       </c>
       <c r="D72" s="8">
-        <v>48212.95</v>
+        <v>64756.5</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B73" s="4">
-        <v>43952</v>
+        <v>44136</v>
       </c>
       <c r="C73" s="5">
-        <v>46343.28</v>
+        <v>50428.65</v>
       </c>
       <c r="D73" s="6">
-        <v>45096.67</v>
+        <v>62255.55</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B74" s="4">
-        <v>43922</v>
+        <v>44105</v>
       </c>
       <c r="C74" s="7">
-        <v>45504.44</v>
+        <v>50697.85</v>
       </c>
       <c r="D74" s="8">
-        <v>42058.33</v>
+        <v>61319.9</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B75" s="4">
-        <v>43891</v>
+        <v>44075</v>
       </c>
       <c r="C75" s="5">
-        <v>42285.33</v>
+        <v>50783.64</v>
       </c>
       <c r="D75" s="6">
-        <v>41382.38</v>
+        <v>63337.05</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B76" s="4">
-        <v>43862</v>
+        <v>44044</v>
       </c>
       <c r="C76" s="7">
-        <v>41195.21</v>
+        <v>52917.19</v>
       </c>
       <c r="D76" s="8">
-        <v>46567.11</v>
+        <v>67717.48</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B77" s="4">
-        <v>43831</v>
+        <v>44013</v>
       </c>
       <c r="C77" s="5">
-        <v>39983.83</v>
+        <v>49878.43</v>
       </c>
       <c r="D77" s="6">
-        <v>46498.48</v>
+        <v>54813.48</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B78" s="4">
-        <v>43800</v>
+        <v>43983</v>
       </c>
       <c r="C78" s="7">
-        <v>38091.571429</v>
+        <v>47314.73</v>
       </c>
       <c r="D78" s="8">
-        <v>44575.714286</v>
+        <v>48212.95</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B79" s="4">
-        <v>43770</v>
+        <v>43952</v>
       </c>
       <c r="C79" s="5">
-        <v>38122.2</v>
+        <v>46343.28</v>
       </c>
       <c r="D79" s="6">
-        <v>44937.5</v>
+        <v>45096.67</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B80" s="4">
-        <v>43739</v>
+        <v>43922</v>
       </c>
       <c r="C80" s="7">
-        <v>38213.55</v>
+        <v>45504.44</v>
       </c>
       <c r="D80" s="8">
-        <v>45578.3</v>
+        <v>42058.33</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B81" s="4">
-        <v>43709</v>
+        <v>43891</v>
       </c>
       <c r="C81" s="5">
-        <v>37926.736842</v>
+        <v>42285.33</v>
       </c>
       <c r="D81" s="6">
-        <v>46681.842105</v>
+        <v>41382.38</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B82" s="4">
-        <v>43678</v>
+        <v>43862</v>
       </c>
       <c r="C82" s="7">
-        <v>37356.15</v>
+        <v>41195.21</v>
       </c>
       <c r="D82" s="8">
-        <v>43746.75</v>
+        <v>46567.11</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B83" s="4">
-        <v>43647</v>
+        <v>43831</v>
       </c>
       <c r="C83" s="5">
-        <v>34522.26087</v>
+        <v>39983.83</v>
       </c>
       <c r="D83" s="6">
-        <v>39098.695652</v>
+        <v>46498.48</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B84" s="4">
-        <v>43617</v>
+        <v>43800</v>
       </c>
       <c r="C84" s="7">
-        <v>33121.263158</v>
+        <v>38091.571429</v>
       </c>
       <c r="D84" s="8">
-        <v>37186.947368</v>
+        <v>44575.714286</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B85" s="4">
-        <v>43586</v>
+        <v>43770</v>
       </c>
       <c r="C85" s="5">
-        <v>31737.545455</v>
+        <v>38122.2</v>
       </c>
       <c r="D85" s="6">
-        <v>36589.772727</v>
+        <v>44937.5</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B86" s="4">
-        <v>43556</v>
+        <v>43739</v>
       </c>
       <c r="C86" s="7">
-        <v>31659.263158</v>
+        <v>38213.55</v>
       </c>
       <c r="D86" s="8">
-        <v>37328.157895</v>
+        <v>45578.3</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B87" s="4">
-        <v>43525</v>
+        <v>43709</v>
       </c>
       <c r="C87" s="5">
-        <v>32036.32</v>
+        <v>37926.736842</v>
       </c>
       <c r="D87" s="6">
-        <v>38043.68</v>
+        <v>46681.842105</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B88" s="4">
-        <v>43497</v>
+        <v>43678</v>
       </c>
       <c r="C88" s="7">
-        <v>33216.5</v>
+        <v>37356.15</v>
       </c>
       <c r="D88" s="8">
-        <v>40058.5</v>
+        <v>43746.75</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B89" s="4">
-        <v>43466</v>
+        <v>43647</v>
       </c>
       <c r="C89" s="5">
-        <v>32230</v>
+        <v>34522.26087</v>
       </c>
       <c r="D89" s="6">
-        <v>39100</v>
+        <v>39098.695652</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B90" s="4">
-        <v>43435</v>
+        <v>43617</v>
       </c>
       <c r="C90" s="7">
-        <v>31250.5</v>
+        <v>33121.263158</v>
       </c>
       <c r="D90" s="8">
-        <v>37094.75</v>
+        <v>37186.947368</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B91" s="4">
-        <v>43405</v>
+        <v>43586</v>
       </c>
       <c r="C91" s="5">
-        <v>31010.368421</v>
+        <v>31737.545455</v>
       </c>
       <c r="D91" s="6">
-        <v>36879.263158</v>
+        <v>36589.772727</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B92" s="4">
-        <v>43374</v>
+        <v>43556</v>
       </c>
       <c r="C92" s="7">
-        <v>31489.285714</v>
+        <v>31659.263158</v>
       </c>
       <c r="D92" s="8">
-        <v>38307.380952</v>
+        <v>37328.157895</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B93" s="4">
-        <v>43344</v>
+        <v>43525</v>
       </c>
       <c r="C93" s="5">
-        <v>30537.777778</v>
+        <v>32036.32</v>
       </c>
       <c r="D93" s="6">
-        <v>36864.166667</v>
+        <v>38043.68</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B94" s="4">
-        <v>43313</v>
+        <v>43497</v>
       </c>
       <c r="C94" s="7">
-        <v>29644.285714</v>
+        <v>33216.5</v>
       </c>
       <c r="D94" s="8">
-        <v>37374.047619</v>
+        <v>40058.5</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B95" s="4">
-        <v>43282</v>
+        <v>43466</v>
       </c>
       <c r="C95" s="5">
-        <v>30097.045455</v>
+        <v>32230</v>
       </c>
       <c r="D95" s="6">
-        <v>38592.272727</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B96" s="4">
-        <v>43252</v>
+        <v>43435</v>
       </c>
       <c r="C96" s="7">
-        <v>30707.142857</v>
+        <v>31250.5</v>
       </c>
       <c r="D96" s="8">
-        <v>39907.142857</v>
+        <v>37094.75</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B97" s="4">
-        <v>43221</v>
+        <v>43405</v>
       </c>
       <c r="C97" s="5">
-        <v>31116.14</v>
+        <v>31010.368421</v>
       </c>
       <c r="D97" s="6">
-        <v>39716.36</v>
+        <v>36879.263158</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B98" s="4">
-        <v>43191</v>
+        <v>43374</v>
       </c>
       <c r="C98" s="7">
-        <v>30985.5</v>
+        <v>31489.285714</v>
       </c>
       <c r="D98" s="8">
-        <v>38913.25</v>
+        <v>38307.380952</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B99" s="4">
-        <v>43160</v>
+        <v>43344</v>
       </c>
       <c r="C99" s="5">
-        <v>30419.72</v>
+        <v>30537.777778</v>
       </c>
       <c r="D99" s="6">
-        <v>38332.22</v>
+        <v>36864.166667</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B100" s="4">
-        <v>43132</v>
+        <v>43313</v>
       </c>
       <c r="C100" s="7">
-        <v>30391.32</v>
+        <v>29644.285714</v>
       </c>
       <c r="D100" s="8">
-        <v>38453.95</v>
+        <v>37374.047619</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B101" s="4">
-        <v>43101</v>
+        <v>43282</v>
       </c>
       <c r="C101" s="5">
-        <v>29854.32</v>
+        <v>30097.045455</v>
       </c>
       <c r="D101" s="6">
-        <v>38931.36</v>
+        <v>38592.272727</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B102" s="4">
-        <v>43070</v>
+        <v>43252</v>
       </c>
       <c r="C102" s="7">
-        <v>28763.42</v>
+        <v>30707.142857</v>
       </c>
       <c r="D102" s="8">
-        <v>37270.26</v>
+        <v>39907.142857</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B103" s="4">
-        <v>43040</v>
+        <v>43221</v>
       </c>
       <c r="C103" s="5">
-        <v>29399.09</v>
+        <v>31116.14</v>
       </c>
       <c r="D103" s="6">
-        <v>39332.27</v>
+        <v>39716.36</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B104" s="4">
-        <v>43009</v>
+        <v>43191</v>
       </c>
       <c r="C104" s="7">
-        <v>29505.3</v>
+        <v>30985.5</v>
       </c>
       <c r="D104" s="8">
-        <v>39385.05</v>
+        <v>38913.25</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B105" s="4">
-        <v>42979</v>
+        <v>43160</v>
       </c>
       <c r="C105" s="5">
-        <v>29899.29</v>
+        <v>30419.72</v>
       </c>
       <c r="D105" s="6">
-        <v>40120</v>
+        <v>38332.22</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B106" s="4">
-        <v>42948</v>
+        <v>43132</v>
       </c>
       <c r="C106" s="7">
-        <v>28893.24</v>
+        <v>30391.32</v>
       </c>
       <c r="D106" s="8">
-        <v>38637.33</v>
+        <v>38453.95</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B107" s="4">
-        <v>42917</v>
+        <v>43101</v>
       </c>
       <c r="C107" s="5">
-        <v>28170.48</v>
+        <v>29854.32</v>
       </c>
       <c r="D107" s="6">
-        <v>37404.29</v>
+        <v>38931.36</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B108" s="4">
-        <v>42887</v>
+        <v>43070</v>
       </c>
       <c r="C108" s="7">
-        <v>28823.1</v>
+        <v>28763.42</v>
       </c>
       <c r="D108" s="8">
-        <v>39491.67</v>
+        <v>37270.26</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B109" s="4">
-        <v>42856</v>
+        <v>43040</v>
       </c>
       <c r="C109" s="5">
-        <v>28471.36</v>
+        <v>29399.09</v>
       </c>
       <c r="D109" s="6">
-        <v>39366.14</v>
+        <v>39332.27</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B110" s="4">
-        <v>42826</v>
+        <v>43009</v>
       </c>
       <c r="C110" s="7">
-        <v>29010.28</v>
+        <v>29505.3</v>
       </c>
       <c r="D110" s="8">
-        <v>42141.67</v>
+        <v>39385.05</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B111" s="4">
-        <v>42795</v>
+        <v>42979</v>
       </c>
       <c r="C111" s="5">
-        <v>28758.18</v>
+        <v>29899.29</v>
       </c>
       <c r="D111" s="6">
-        <v>42100.23</v>
+        <v>40120</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B112" s="4">
-        <v>42767</v>
+        <v>42948</v>
       </c>
       <c r="C112" s="7">
-        <v>29264.74</v>
+        <v>28893.24</v>
       </c>
       <c r="D112" s="8">
-        <v>42914.47</v>
+        <v>38637.33</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B113" s="4">
-        <v>42736</v>
+        <v>42917</v>
       </c>
       <c r="C113" s="5">
-        <v>28745.95</v>
+        <v>28170.48</v>
       </c>
       <c r="D113" s="6">
-        <v>41139.76</v>
+        <v>37404.29</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B114" s="4">
-        <v>42705</v>
+        <v>42887</v>
       </c>
       <c r="C114" s="7">
-        <v>27754.29</v>
+        <v>28823.1</v>
       </c>
       <c r="D114" s="8">
-        <v>40288.81</v>
+        <v>39491.67</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B115" s="4">
-        <v>42675</v>
+        <v>42856</v>
       </c>
       <c r="C115" s="5">
-        <v>29796.43</v>
+        <v>28471.36</v>
       </c>
       <c r="D115" s="6">
-        <v>42971.9</v>
+        <v>39366.14</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B116" s="4">
-        <v>42644</v>
+        <v>42826</v>
       </c>
       <c r="C116" s="7">
-        <v>30071.37</v>
+        <v>29010.28</v>
       </c>
       <c r="D116" s="8">
-        <v>43230.05</v>
+        <v>42141.67</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B117" s="4">
-        <v>42614</v>
+        <v>42795</v>
       </c>
       <c r="C117" s="5">
-        <v>31178</v>
+        <v>28758.18</v>
       </c>
       <c r="D117" s="6">
-        <v>46233.5</v>
+        <v>42100.23</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B118" s="4">
-        <v>42583</v>
+        <v>42767</v>
       </c>
       <c r="C118" s="7">
-        <v>31270</v>
+        <v>29264.74</v>
       </c>
       <c r="D118" s="8">
-        <v>46614.09</v>
+        <v>42914.47</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B119" s="4">
-        <v>42552</v>
+        <v>42736</v>
       </c>
       <c r="C119" s="5">
-        <v>30941.75</v>
+        <v>28745.95</v>
       </c>
       <c r="D119" s="6">
-        <v>46942.5</v>
+        <v>41139.76</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B120" s="4">
-        <v>42522</v>
+        <v>42705</v>
       </c>
       <c r="C120" s="7">
-        <v>29745.45</v>
+        <v>27754.29</v>
       </c>
       <c r="D120" s="8">
-        <v>41195.91</v>
+        <v>40288.81</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B121" s="4">
-        <v>42491</v>
+        <v>42675</v>
       </c>
       <c r="C121" s="5">
-        <v>29639.09</v>
+        <v>29796.43</v>
       </c>
       <c r="D121" s="6">
-        <v>40692.5</v>
+        <v>42971.9</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B122" s="4">
-        <v>42461</v>
+        <v>42644</v>
       </c>
       <c r="C122" s="7">
-        <v>28818.16</v>
+        <v>30071.37</v>
       </c>
       <c r="D122" s="8">
-        <v>38656.05</v>
+        <v>43230.05</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B123" s="4">
-        <v>42430</v>
+        <v>42614</v>
       </c>
       <c r="C123" s="5">
-        <v>28794.25</v>
+        <v>31178</v>
       </c>
       <c r="D123" s="6">
-        <v>37499.5</v>
+        <v>46233.5</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B124" s="4">
-        <v>42401</v>
+        <v>42583</v>
       </c>
       <c r="C124" s="7">
-        <v>28251.67</v>
+        <v>31270</v>
       </c>
       <c r="D124" s="8">
-        <v>36916.9</v>
+        <v>46614.09</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B125" s="4">
-        <v>42370</v>
+        <v>42552</v>
       </c>
       <c r="C125" s="5">
-        <v>25997.5</v>
+        <v>30941.75</v>
       </c>
       <c r="D125" s="6">
-        <v>34287.25</v>
+        <v>46942.5</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B126" s="4">
-        <v>42339</v>
+        <v>42522</v>
       </c>
       <c r="C126" s="7">
-        <v>25207.38</v>
+        <v>29745.45</v>
       </c>
       <c r="D126" s="8">
-        <v>34245.24</v>
+        <v>41195.91</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B127" s="4">
-        <v>42309</v>
+        <v>42491</v>
       </c>
       <c r="C127" s="5">
-        <v>25648.39</v>
+        <v>29639.09</v>
       </c>
       <c r="D127" s="6">
-        <v>35340.06</v>
+        <v>40692.5</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B128" s="4">
-        <v>42278</v>
+        <v>42461</v>
       </c>
       <c r="C128" s="7">
-        <v>26576.59</v>
+        <v>28818.16</v>
       </c>
       <c r="D128" s="8">
-        <v>37207.5</v>
+        <v>38656.05</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B129" s="4">
-        <v>42248</v>
+        <v>42430</v>
       </c>
       <c r="C129" s="5">
-        <v>26245.83</v>
+        <v>28794.25</v>
       </c>
       <c r="D129" s="6">
-        <v>35601.04</v>
+        <v>37499.5</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B130" s="4">
-        <v>42217</v>
+        <v>42401</v>
       </c>
       <c r="C130" s="7">
-        <v>25728.54</v>
+        <v>28251.67</v>
       </c>
       <c r="D130" s="8">
-        <v>35499.79</v>
+        <v>36916.9</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B131" s="4">
-        <v>42186</v>
+        <v>42370</v>
       </c>
       <c r="C131" s="5">
-        <v>25539.38</v>
+        <v>25997.5</v>
       </c>
       <c r="D131" s="6">
-        <v>35257.29</v>
+        <v>34287.25</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B132" s="4">
-        <v>42156</v>
+        <v>42339</v>
       </c>
       <c r="C132" s="7">
-        <v>26645.96</v>
+        <v>25207.38</v>
       </c>
       <c r="D132" s="8">
-        <v>37481.15</v>
+        <v>34245.24</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B133" s="4">
-        <v>42125</v>
+        <v>42309</v>
       </c>
       <c r="C133" s="5">
-        <v>27093.04</v>
+        <v>25648.39</v>
       </c>
       <c r="D133" s="6">
-        <v>38990.65</v>
+        <v>35340.06</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B134" s="4">
-        <v>42095</v>
+        <v>42278</v>
       </c>
       <c r="C134" s="7">
-        <v>26682.61</v>
+        <v>26576.59</v>
       </c>
       <c r="D134" s="8">
-        <v>37490.87</v>
+        <v>37207.5</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B135" s="4">
-        <v>42064</v>
+        <v>42248</v>
       </c>
       <c r="C135" s="5">
-        <v>26167.83</v>
+        <v>26245.83</v>
       </c>
       <c r="D135" s="6">
-        <v>37176.3</v>
+        <v>35601.04</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B136" s="4">
-        <v>42036</v>
+        <v>42217</v>
       </c>
       <c r="C136" s="7">
-        <v>27075.48</v>
+        <v>25728.54</v>
       </c>
       <c r="D136" s="8">
-        <v>38262.38</v>
+        <v>35499.79</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B137" s="4">
-        <v>42005</v>
+        <v>42186</v>
       </c>
       <c r="C137" s="5">
-        <v>27403.27</v>
+        <v>25539.38</v>
       </c>
       <c r="D137" s="6">
-        <v>38526.35</v>
+        <v>35257.29</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B138" s="4">
-        <v>41974</v>
+        <v>42156</v>
       </c>
       <c r="C138" s="7">
-        <v>26678.27</v>
+        <v>26645.96</v>
       </c>
       <c r="D138" s="8">
-        <v>37454.81</v>
+        <v>37481.15</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B139" s="4">
-        <v>41944</v>
+        <v>42125</v>
       </c>
       <c r="C139" s="5">
-        <v>26115</v>
+        <v>27093.04</v>
       </c>
       <c r="D139" s="6">
-        <v>36593.33</v>
+        <v>38990.65</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B140" s="4">
-        <v>41913</v>
+        <v>42095</v>
       </c>
       <c r="C140" s="7">
-        <v>26990.73</v>
+        <v>26682.61</v>
       </c>
       <c r="D140" s="8">
-        <v>39185.73</v>
+        <v>37490.87</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B141" s="4">
-        <v>41883</v>
+        <v>42064</v>
       </c>
       <c r="C141" s="5">
-        <v>26962.6</v>
+        <v>26167.83</v>
       </c>
       <c r="D141" s="6">
-        <v>41390.4</v>
+        <v>37176.3</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B142" s="4">
-        <v>41852</v>
+        <v>42036</v>
       </c>
       <c r="C142" s="7">
-        <v>28079.57</v>
+        <v>27075.48</v>
       </c>
       <c r="D142" s="8">
-        <v>43969.13</v>
+        <v>38262.38</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B143" s="4">
-        <v>41821</v>
+        <v>42005</v>
       </c>
       <c r="C143" s="5">
-        <v>28007.59</v>
+        <v>27403.27</v>
       </c>
       <c r="D143" s="6">
-        <v>45450.19</v>
+        <v>38526.35</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B144" s="4">
-        <v>41791</v>
+        <v>41974</v>
       </c>
       <c r="C144" s="7">
-        <v>27427.4</v>
+        <v>26678.27</v>
       </c>
       <c r="D144" s="8">
-        <v>42970.2</v>
+        <v>37454.81</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B145" s="4">
-        <v>41760</v>
+        <v>41944</v>
       </c>
       <c r="C145" s="5">
-        <v>28738</v>
+        <v>26115</v>
       </c>
       <c r="D145" s="6">
-        <v>42116.2</v>
+        <v>36593.33</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B146" s="4">
-        <v>41730</v>
+        <v>41913</v>
       </c>
       <c r="C146" s="7">
-        <v>29328.91</v>
+        <v>26990.73</v>
       </c>
       <c r="D146" s="8">
-        <v>43606.74</v>
+        <v>39185.73</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B147" s="4">
-        <v>41699</v>
+        <v>41883</v>
       </c>
       <c r="C147" s="5">
-        <v>29831.88</v>
+        <v>26962.6</v>
       </c>
       <c r="D147" s="6">
-        <v>45978.13</v>
+        <v>41390.4</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B148" s="4">
-        <v>41671</v>
+        <v>41852</v>
       </c>
       <c r="C148" s="7">
-        <v>30210.68</v>
+        <v>28079.57</v>
       </c>
       <c r="D148" s="8">
-        <v>46382.95</v>
+        <v>43969.13</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B149" s="4">
-        <v>41640</v>
+        <v>41821</v>
       </c>
       <c r="C149" s="5">
-        <v>29581.85</v>
+        <v>28007.59</v>
       </c>
       <c r="D149" s="6">
-        <v>45120.74</v>
+        <v>45450.19</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B150" s="4">
-        <v>41609</v>
+        <v>41791</v>
       </c>
       <c r="C150" s="7">
-        <v>29904.2</v>
+        <v>27427.4</v>
       </c>
       <c r="D150" s="8">
-        <v>44533.6</v>
+        <v>42970.2</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B151" s="4">
-        <v>41579</v>
+        <v>41760</v>
       </c>
       <c r="C151" s="5">
-        <v>30739.6</v>
+        <v>28738</v>
       </c>
       <c r="D151" s="6">
-        <v>47877</v>
+        <v>42116.2</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B152" s="4">
-        <v>41548</v>
+        <v>41730</v>
       </c>
       <c r="C152" s="7">
-        <v>30709.63</v>
+        <v>29328.91</v>
       </c>
       <c r="D152" s="8">
-        <v>49512.59</v>
+        <v>43606.74</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B153" s="4">
-        <v>41518</v>
+        <v>41699</v>
       </c>
       <c r="C153" s="5">
-        <v>30473.04</v>
+        <v>29831.88</v>
       </c>
       <c r="D153" s="6">
-        <v>52250.87</v>
+        <v>45978.13</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B154" s="4">
-        <v>41487</v>
+        <v>41671</v>
       </c>
       <c r="C154" s="7">
-        <v>30216.3</v>
+        <v>30210.68</v>
       </c>
       <c r="D154" s="8">
-        <v>48806.52</v>
+        <v>46382.95</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B155" s="4">
-        <v>41456</v>
+        <v>41640</v>
       </c>
       <c r="C155" s="5">
-        <v>26928.15</v>
+        <v>29581.85</v>
       </c>
       <c r="D155" s="6">
-        <v>41634.07</v>
+        <v>45120.74</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B156" s="4">
-        <v>41426</v>
+        <v>41609</v>
       </c>
       <c r="C156" s="7">
-        <v>27178.13</v>
+        <v>29904.2</v>
       </c>
       <c r="D156" s="8">
-        <v>43663.54</v>
+        <v>44533.6</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B157" s="4">
-        <v>41395</v>
+        <v>41579</v>
       </c>
       <c r="C157" s="5">
-        <v>26768.65</v>
+        <v>30739.6</v>
       </c>
       <c r="D157" s="6">
-        <v>45036.54</v>
+        <v>47877</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B158" s="4">
-        <v>41365</v>
+        <v>41548</v>
       </c>
       <c r="C158" s="7">
-        <v>27742.6</v>
+        <v>30709.63</v>
       </c>
       <c r="D158" s="8">
-        <v>48845</v>
+        <v>49512.59</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B159" s="4">
-        <v>41334</v>
+        <v>41518</v>
       </c>
       <c r="C159" s="5">
-        <v>29513.75</v>
+        <v>30473.04</v>
       </c>
       <c r="D159" s="6">
-        <v>54995</v>
+        <v>52250.87</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B160" s="4">
-        <v>41306</v>
+        <v>41487</v>
       </c>
       <c r="C160" s="7">
-        <v>29963.48</v>
+        <v>30216.3</v>
       </c>
       <c r="D160" s="8">
-        <v>57311.3</v>
+        <v>48806.52</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B161" s="4">
-        <v>41275</v>
+        <v>41456</v>
       </c>
       <c r="C161" s="5">
-        <v>30520.19</v>
+        <v>26928.15</v>
       </c>
       <c r="D161" s="6">
-        <v>58731.73</v>
+        <v>41634.07</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B162" s="4">
-        <v>41244</v>
+        <v>41426</v>
       </c>
       <c r="C162" s="7">
-        <v>30832.8</v>
+        <v>27178.13</v>
       </c>
       <c r="D162" s="8">
-        <v>60633.64</v>
+        <v>43663.54</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B163" s="4">
-        <v>41214</v>
+        <v>41395</v>
       </c>
       <c r="C163" s="5">
-        <v>31547.95</v>
+        <v>26768.65</v>
       </c>
       <c r="D163" s="6">
-        <v>61848.18</v>
+        <v>45036.54</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B164" s="4">
-        <v>41183</v>
+        <v>41365</v>
       </c>
       <c r="C164" s="7">
-        <v>31055.63</v>
+        <v>27742.6</v>
       </c>
       <c r="D164" s="8">
-        <v>61072.08</v>
+        <v>48845</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B165" s="4">
-        <v>41153</v>
+        <v>41334</v>
       </c>
       <c r="C165" s="5">
-        <v>31672.83</v>
+        <v>29513.75</v>
       </c>
       <c r="D165" s="6">
-        <v>62134.57</v>
+        <v>54995</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B166" s="4">
-        <v>41122</v>
+        <v>41306</v>
       </c>
       <c r="C166" s="7">
-        <v>30179.79</v>
+        <v>29963.48</v>
       </c>
       <c r="D166" s="8">
-        <v>55627.5</v>
+        <v>57311.3</v>
       </c>
     </row>
     <row r="167" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B167" s="4">
-        <v>41091</v>
+        <v>41275</v>
       </c>
       <c r="C167" s="5">
-        <v>29468.46</v>
+        <v>30520.19</v>
       </c>
       <c r="D167" s="6">
-        <v>53061.35</v>
+        <v>58731.73</v>
       </c>
     </row>
     <row r="168" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B168" s="4">
-        <v>41061</v>
+        <v>41244</v>
       </c>
       <c r="C168" s="7">
-        <v>29818.62</v>
+        <v>30832.8</v>
       </c>
       <c r="D168" s="8">
-        <v>54598.65</v>
+        <v>60633.64</v>
       </c>
     </row>
     <row r="169" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B169" s="4">
-        <v>41030</v>
+        <v>41214</v>
       </c>
       <c r="C169" s="5">
-        <v>28830.96</v>
+        <v>31547.95</v>
       </c>
       <c r="D169" s="6">
-        <v>54536.15</v>
+        <v>61848.18</v>
       </c>
     </row>
     <row r="170" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B170" s="4">
-        <v>41000</v>
+        <v>41183</v>
       </c>
       <c r="C170" s="7">
-        <v>28562.73</v>
+        <v>31055.63</v>
       </c>
       <c r="D170" s="8">
-        <v>56677.5</v>
+        <v>61072.08</v>
       </c>
     </row>
     <row r="171" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B171" s="4">
-        <v>40969</v>
+        <v>41153</v>
       </c>
       <c r="C171" s="5">
-        <v>27853.95</v>
+        <v>31672.83</v>
       </c>
       <c r="D171" s="6">
-        <v>57579.47</v>
+        <v>62134.57</v>
       </c>
     </row>
     <row r="172" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B172" s="4">
-        <v>40940</v>
+        <v>41122</v>
       </c>
       <c r="C172" s="7">
-        <v>28118.7</v>
+        <v>30179.79</v>
       </c>
       <c r="D172" s="8">
-        <v>56766.96</v>
+        <v>55627.5</v>
       </c>
     </row>
     <row r="173" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B173" s="4">
-        <v>40909</v>
+        <v>41091</v>
       </c>
       <c r="C173" s="5">
-        <v>27597.8</v>
+        <v>29468.46</v>
       </c>
       <c r="D173" s="6">
-        <v>53495.8</v>
+        <v>53061.35</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B174" s="4">
-        <v>40878</v>
+        <v>41061</v>
       </c>
       <c r="C174" s="7">
-        <v>28062.96</v>
+        <v>29818.62</v>
       </c>
       <c r="D174" s="8">
-        <v>53995.93</v>
+        <v>54598.65</v>
       </c>
     </row>
     <row r="175" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B175" s="4">
-        <v>40848</v>
+        <v>41030</v>
       </c>
       <c r="C175" s="5">
-        <v>28562.92</v>
+        <v>28830.96</v>
       </c>
       <c r="D175" s="6">
-        <v>56513.75</v>
+        <v>54536.15</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B176" s="4">
-        <v>40817</v>
+        <v>41000</v>
       </c>
       <c r="C176" s="7">
-        <v>26667.5</v>
+        <v>28562.73</v>
       </c>
       <c r="D176" s="8">
-        <v>53689.17</v>
+        <v>56677.5</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B177" s="4">
-        <v>40787</v>
+        <v>40969</v>
       </c>
       <c r="C177" s="5">
-        <v>27486.8</v>
+        <v>27853.95</v>
       </c>
       <c r="D177" s="6">
-        <v>61431.8</v>
+        <v>57579.47</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B178" s="4">
-        <v>40756</v>
+        <v>40940</v>
       </c>
       <c r="C178" s="7">
-        <v>25877.92</v>
+        <v>28118.7</v>
       </c>
       <c r="D178" s="8">
-        <v>61275.6</v>
+        <v>56766.96</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B179" s="4">
-        <v>40725</v>
+        <v>40909</v>
       </c>
       <c r="C179" s="5">
-        <v>22627.4</v>
+        <v>27597.8</v>
       </c>
       <c r="D179" s="6">
-        <v>56227</v>
+        <v>53495.8</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B180" s="4">
-        <v>40695</v>
+        <v>40878</v>
       </c>
       <c r="C180" s="7">
-        <v>22213.85</v>
+        <v>28062.96</v>
       </c>
       <c r="D180" s="8">
-        <v>54497.12</v>
+        <v>53995.93</v>
       </c>
     </row>
     <row r="181" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B181" s="4">
-        <v>40664</v>
+        <v>40848</v>
       </c>
       <c r="C181" s="5">
-        <v>22129.5</v>
+        <v>28562.92</v>
       </c>
       <c r="D181" s="6">
-        <v>57048.46</v>
+        <v>56513.75</v>
       </c>
     </row>
     <row r="182" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B182" s="4">
-        <v>40634</v>
+        <v>40817</v>
       </c>
       <c r="C182" s="7">
-        <v>21469.78</v>
+        <v>26667.5</v>
       </c>
       <c r="D182" s="8">
-        <v>65269.35</v>
+        <v>53689.17</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B183" s="4">
-        <v>40603</v>
+        <v>40787</v>
       </c>
       <c r="C183" s="5">
-        <v>20835</v>
+        <v>27486.8</v>
       </c>
       <c r="D183" s="6">
-        <v>54484.08</v>
+        <v>61431.8</v>
       </c>
     </row>
     <row r="184" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B184" s="4">
-        <v>40575</v>
+        <v>40756</v>
       </c>
       <c r="C184" s="7">
-        <v>20321.09</v>
+        <v>25877.92</v>
       </c>
       <c r="D184" s="8">
-        <v>46825.45</v>
+        <v>61275.6</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B185" s="4">
-        <v>40544</v>
+        <v>40725</v>
       </c>
       <c r="C185" s="5">
-        <v>20203.8</v>
+        <v>22627.4</v>
       </c>
       <c r="D185" s="6">
-        <v>44807.4</v>
+        <v>56227</v>
       </c>
     </row>
     <row r="186" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B186" s="4">
-        <v>40513</v>
+        <v>40695</v>
       </c>
       <c r="C186" s="7">
-        <v>20506.3</v>
+        <v>22213.85</v>
       </c>
       <c r="D186" s="8">
-        <v>45349.81</v>
+        <v>54497.12</v>
       </c>
     </row>
     <row r="187" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B187" s="4">
-        <v>40483</v>
+        <v>40664</v>
       </c>
       <c r="C187" s="5">
-        <v>20140.21</v>
+        <v>22129.5</v>
       </c>
       <c r="D187" s="6">
-        <v>41124.5</v>
+        <v>57048.46</v>
       </c>
     </row>
     <row r="188" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B188" s="4">
-        <v>40452</v>
+        <v>40634</v>
       </c>
       <c r="C188" s="7">
-        <v>19474.23</v>
+        <v>21469.78</v>
       </c>
       <c r="D188" s="8">
-        <v>35943.85</v>
+        <v>65269.35</v>
       </c>
     </row>
     <row r="189" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B189" s="4">
-        <v>40422</v>
+        <v>40603</v>
       </c>
       <c r="C189" s="5">
-        <v>19055.63</v>
+        <v>20835</v>
       </c>
       <c r="D189" s="6">
-        <v>32519.33</v>
+        <v>54484.08</v>
       </c>
     </row>
     <row r="190" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B190" s="4">
-        <v>40391</v>
+        <v>40575</v>
       </c>
       <c r="C190" s="7">
-        <v>18457.2</v>
+        <v>20321.09</v>
       </c>
       <c r="D190" s="8">
-        <v>29828</v>
+        <v>46825.45</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B191" s="4">
-        <v>40360</v>
+        <v>40544</v>
       </c>
       <c r="C191" s="5">
-        <v>18269.81</v>
+        <v>20203.8</v>
       </c>
       <c r="D191" s="6">
-        <v>29368.08</v>
+        <v>44807.4</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B192" s="4">
-        <v>40330</v>
+        <v>40513</v>
       </c>
       <c r="C192" s="7">
-        <v>18744.62</v>
+        <v>20506.3</v>
       </c>
       <c r="D192" s="8">
-        <v>29821.35</v>
+        <v>45349.81</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B193" s="4">
-        <v>40299</v>
+        <v>40483</v>
       </c>
       <c r="C193" s="5">
-        <v>18024.2</v>
+        <v>20140.21</v>
       </c>
       <c r="D193" s="6">
-        <v>29342.2</v>
+        <v>41124.5</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B194" s="4">
-        <v>40269</v>
+        <v>40452</v>
       </c>
       <c r="C194" s="7">
-        <v>16692.92</v>
+        <v>19474.23</v>
       </c>
       <c r="D194" s="8">
-        <v>28060.42</v>
+        <v>35943.85</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B195" s="4">
-        <v>40238</v>
+        <v>40422</v>
       </c>
       <c r="C195" s="5">
-        <v>16613.96</v>
+        <v>19055.63</v>
       </c>
       <c r="D195" s="6">
-        <v>27086.25</v>
+        <v>32519.33</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B196" s="4">
-        <v>40210</v>
+        <v>40391</v>
       </c>
       <c r="C196" s="7">
-        <v>16525.43</v>
+        <v>18457.2</v>
       </c>
       <c r="D196" s="8">
-        <v>25608.48</v>
+        <v>29828</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B197" s="4">
-        <v>40179</v>
+        <v>40360</v>
       </c>
       <c r="C197" s="5">
-        <v>16705.8</v>
+        <v>18269.81</v>
       </c>
       <c r="D197" s="6">
-        <v>28027.6</v>
+        <v>29368.08</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B198" s="4">
-        <v>40148</v>
+        <v>40330</v>
       </c>
       <c r="C198" s="7">
-        <v>17159.42</v>
+        <v>18744.62</v>
       </c>
       <c r="D198" s="8">
-        <v>28363.08</v>
+        <v>29821.35</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B199" s="4">
-        <v>40118</v>
+        <v>40299</v>
       </c>
       <c r="C199" s="5">
-        <v>17056.8</v>
+        <v>18024.2</v>
       </c>
       <c r="D199" s="6">
-        <v>28264</v>
+        <v>29342.2</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B200" s="4">
-        <v>40087</v>
+        <v>40269</v>
       </c>
       <c r="C200" s="7">
-        <v>15882.39</v>
+        <v>16692.92</v>
       </c>
       <c r="D200" s="8">
-        <v>27322.61</v>
+        <v>28060.42</v>
       </c>
     </row>
     <row r="201" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B201" s="4">
-        <v>40057</v>
+        <v>40238</v>
       </c>
       <c r="C201" s="5">
-        <v>15722.61</v>
+        <v>16613.96</v>
       </c>
       <c r="D201" s="6">
-        <v>26220.87</v>
+        <v>27086.25</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B202" s="4">
-        <v>40026</v>
+        <v>40210</v>
       </c>
       <c r="C202" s="7">
-        <v>14952.08</v>
+        <v>16525.43</v>
       </c>
       <c r="D202" s="8">
-        <v>23583.54</v>
+        <v>25608.48</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B203" s="4">
-        <v>39995</v>
+        <v>40179</v>
       </c>
       <c r="C203" s="5">
-        <v>14720.37</v>
+        <v>16705.8</v>
       </c>
       <c r="D203" s="6">
-        <v>22375.74</v>
+        <v>28027.6</v>
       </c>
     </row>
     <row r="204" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B204" s="4">
-        <v>39965</v>
+        <v>40148</v>
       </c>
       <c r="C204" s="7">
-        <v>14638.85</v>
+        <v>17159.42</v>
       </c>
       <c r="D204" s="8">
-        <v>23069.54</v>
+        <v>28363.08</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B205" s="4">
-        <v>39934</v>
+        <v>40118</v>
       </c>
       <c r="C205" s="5">
-        <v>14620.83</v>
+        <v>17056.8</v>
       </c>
       <c r="D205" s="6">
-        <v>22587.08</v>
+        <v>28264</v>
       </c>
     </row>
     <row r="206" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B206" s="4">
-        <v>39904</v>
+        <v>40087</v>
       </c>
       <c r="C206" s="7">
-        <v>14474.57</v>
+        <v>15882.39</v>
       </c>
       <c r="D206" s="8">
-        <v>21339.52</v>
+        <v>27322.61</v>
       </c>
     </row>
     <row r="207" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B207" s="4">
-        <v>39873</v>
+        <v>40057</v>
       </c>
       <c r="C207" s="5">
-        <v>15232.2</v>
+        <v>15722.61</v>
       </c>
       <c r="D207" s="6">
-        <v>22201.2</v>
+        <v>26220.87</v>
       </c>
     </row>
     <row r="208" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B208" s="4">
-        <v>39845</v>
+        <v>40026</v>
       </c>
       <c r="C208" s="7">
-        <v>14800.22</v>
+        <v>14952.08</v>
       </c>
       <c r="D208" s="8">
-        <v>21448.26</v>
+        <v>23583.54</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B209" s="4">
-        <v>39814</v>
+        <v>39995</v>
       </c>
       <c r="C209" s="5">
-        <v>13472.8</v>
+        <v>14720.37</v>
       </c>
       <c r="D209" s="6">
-        <v>18710.4</v>
+        <v>22375.74</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B210" s="4">
-        <v>39783</v>
+        <v>39965</v>
       </c>
       <c r="C210" s="7">
-        <v>12922.6</v>
+        <v>14638.85</v>
       </c>
       <c r="D210" s="8">
-        <v>17350.4</v>
+        <v>23069.54</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B211" s="4">
-        <v>39753</v>
+        <v>39934</v>
       </c>
       <c r="C211" s="5">
-        <v>12142.92</v>
+        <v>14620.83</v>
       </c>
       <c r="D211" s="6">
-        <v>17210.43</v>
+        <v>22587.08</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B212" s="4">
-        <v>39722</v>
+        <v>39904</v>
       </c>
       <c r="C212" s="7">
-        <v>12690.87</v>
+        <v>14474.57</v>
       </c>
       <c r="D212" s="8">
-        <v>18637.61</v>
+        <v>21339.52</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B213" s="4">
-        <v>39692</v>
+        <v>39873</v>
       </c>
       <c r="C213" s="5">
-        <v>12220.28</v>
+        <v>15232.2</v>
       </c>
       <c r="D213" s="6">
-        <v>20141.71</v>
+        <v>22201.2</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B214" s="4">
-        <v>39661</v>
+        <v>39845</v>
       </c>
       <c r="C214" s="7">
-        <v>11860.64</v>
+        <v>14800.22</v>
       </c>
       <c r="D214" s="8">
-        <v>22172.68</v>
+        <v>21448.26</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B215" s="4">
-        <v>39630</v>
+        <v>39814</v>
       </c>
       <c r="C215" s="5">
-        <v>13027.96</v>
+        <v>13472.8</v>
       </c>
       <c r="D215" s="6">
-        <v>25624.37</v>
+        <v>18710.4</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B216" s="4">
-        <v>39600</v>
+        <v>39783</v>
       </c>
       <c r="C216" s="7">
-        <v>12353</v>
+        <v>12922.6</v>
       </c>
       <c r="D216" s="8">
-        <v>24204</v>
+        <v>17350.4</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B217" s="4">
-        <v>39569</v>
+        <v>39753</v>
       </c>
       <c r="C217" s="5">
-        <v>12143</v>
+        <v>12142.92</v>
       </c>
       <c r="D217" s="6">
-        <v>23795.63</v>
+        <v>17210.43</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B218" s="4">
-        <v>39539</v>
+        <v>39722</v>
       </c>
       <c r="C218" s="7">
-        <v>11810.42</v>
+        <v>12690.87</v>
       </c>
       <c r="D218" s="8">
-        <v>23474.17</v>
+        <v>18637.61</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B219" s="4">
-        <v>39508</v>
+        <v>39692</v>
       </c>
       <c r="C219" s="5">
-        <v>12631.74</v>
+        <v>12220.28</v>
       </c>
       <c r="D219" s="6">
-        <v>24357.05</v>
+        <v>20141.71</v>
       </c>
     </row>
     <row r="220" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B220" s="4">
-        <v>39479</v>
+        <v>39661</v>
       </c>
       <c r="C220" s="7">
-        <v>11887.83</v>
+        <v>11860.64</v>
       </c>
       <c r="D220" s="8">
-        <v>21978.96</v>
+        <v>22172.68</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B221" s="4">
-        <v>39448</v>
+        <v>39630</v>
       </c>
       <c r="C221" s="5">
-        <v>11290.96</v>
+        <v>13027.96</v>
       </c>
       <c r="D221" s="6">
-        <v>20405.38</v>
+        <v>25624.37</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B222" s="4">
-        <v>39417</v>
+        <v>39600</v>
       </c>
       <c r="C222" s="7">
-        <v>10311</v>
+        <v>12353</v>
       </c>
       <c r="D222" s="8">
-        <v>19056</v>
+        <v>24204</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B223" s="4">
-        <v>39387</v>
+        <v>39569</v>
       </c>
       <c r="C223" s="5">
-        <v>10340.38</v>
+        <v>12143</v>
       </c>
       <c r="D223" s="6">
-        <v>19573.46</v>
+        <v>23795.63</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B224" s="4">
-        <v>39356</v>
+        <v>39539</v>
       </c>
       <c r="C224" s="7">
-        <v>9690.96</v>
+        <v>11810.42</v>
       </c>
       <c r="D224" s="8">
-        <v>18385</v>
+        <v>23474.17</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B225" s="4">
-        <v>39326</v>
+        <v>39508</v>
       </c>
       <c r="C225" s="5">
-        <v>9310.96</v>
+        <v>12631.74</v>
       </c>
       <c r="D225" s="6">
-        <v>17651.09</v>
+        <v>24357.05</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B226" s="4">
-        <v>39295</v>
+        <v>39479</v>
       </c>
       <c r="C226" s="7">
-        <v>8835.58</v>
+        <v>11887.83</v>
       </c>
       <c r="D226" s="8">
-        <v>17406.73</v>
+        <v>21978.96</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B227" s="4">
-        <v>39264</v>
+        <v>39448</v>
       </c>
       <c r="C227" s="5">
-        <v>8741.35</v>
+        <v>11290.96</v>
       </c>
       <c r="D227" s="6">
-        <v>17814.54</v>
+        <v>20405.38</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B228" s="4">
-        <v>39234</v>
+        <v>39417</v>
       </c>
       <c r="C228" s="7">
-        <v>8707.42</v>
+        <v>10311</v>
       </c>
       <c r="D228" s="8">
-        <v>18286.73</v>
+        <v>19056</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B229" s="4">
-        <v>39203</v>
+        <v>39387</v>
       </c>
       <c r="C229" s="5">
-        <v>8878.13</v>
+        <v>10340.38</v>
       </c>
       <c r="D229" s="6">
-        <v>18537.29</v>
+        <v>19573.46</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B230" s="4">
-        <v>39173</v>
+        <v>39356</v>
       </c>
       <c r="C230" s="7">
-        <v>9321.09</v>
+        <v>9690.96</v>
       </c>
       <c r="D230" s="8">
-        <v>19677.17</v>
+        <v>18385</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B231" s="4">
-        <v>39142</v>
+        <v>39326</v>
       </c>
       <c r="C231" s="5">
-        <v>9369.6</v>
+        <v>9310.96</v>
       </c>
       <c r="D231" s="6">
-        <v>19494.24</v>
+        <v>17651.09</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B232" s="4">
-        <v>39114</v>
+        <v>39295</v>
       </c>
       <c r="C232" s="7">
-        <v>9545</v>
+        <v>8835.58</v>
       </c>
       <c r="D232" s="8">
-        <v>20323.81</v>
+        <v>17406.73</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B233" s="4">
-        <v>39083</v>
+        <v>39264</v>
       </c>
       <c r="C233" s="5">
-        <v>9069.17</v>
+        <v>8741.35</v>
       </c>
       <c r="D233" s="6">
-        <v>19356.25</v>
+        <v>17814.54</v>
       </c>
     </row>
     <row r="234" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B234" s="4">
-        <v>39052</v>
+        <v>39234</v>
       </c>
       <c r="C234" s="7">
-        <v>9133.13</v>
+        <v>8707.42</v>
       </c>
       <c r="D234" s="8">
-        <v>19912.92</v>
+        <v>18286.73</v>
       </c>
     </row>
     <row r="235" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B235" s="4">
-        <v>39022</v>
+        <v>39203</v>
       </c>
       <c r="C235" s="5">
-        <v>9139.92</v>
+        <v>8878.13</v>
       </c>
       <c r="D235" s="6">
-        <v>19351.38</v>
+        <v>18537.29</v>
       </c>
     </row>
     <row r="236" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B236" s="4">
-        <v>38991</v>
+        <v>39173</v>
       </c>
       <c r="C236" s="7">
-        <v>8694.86</v>
+        <v>9321.09</v>
       </c>
       <c r="D236" s="8">
-        <v>18263.9</v>
+        <v>19677.17</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B237" s="4">
-        <v>38961</v>
+        <v>39142</v>
       </c>
       <c r="C237" s="5">
-        <v>8998.2</v>
+        <v>9369.6</v>
       </c>
       <c r="D237" s="6">
-        <v>18587.4</v>
+        <v>19494.24</v>
       </c>
     </row>
     <row r="238" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B238" s="4">
-        <v>38930</v>
+        <v>39114</v>
       </c>
       <c r="C238" s="7">
-        <v>9468.93</v>
+        <v>9545</v>
       </c>
       <c r="D238" s="8">
-        <v>18981.6</v>
+        <v>20323.81</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B239" s="4">
-        <v>38899</v>
+        <v>39083</v>
       </c>
       <c r="C239" s="5">
-        <v>9559</v>
+        <v>9069.17</v>
       </c>
       <c r="D239" s="6">
-        <v>17786.2</v>
+        <v>19356.25</v>
       </c>
     </row>
     <row r="240" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B240" s="4">
-        <v>38869</v>
+        <v>39052</v>
       </c>
       <c r="C240" s="7">
-        <v>8951.92</v>
+        <v>9133.13</v>
       </c>
       <c r="D240" s="8">
-        <v>16752.12</v>
+        <v>19912.92</v>
       </c>
     </row>
     <row r="241" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B241" s="4">
-        <v>38838</v>
+        <v>39022</v>
       </c>
       <c r="C241" s="5">
-        <v>9969.39</v>
+        <v>9139.92</v>
       </c>
       <c r="D241" s="6">
-        <v>20324.04</v>
+        <v>19351.38</v>
       </c>
     </row>
     <row r="242" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B242" s="4">
-        <v>38808</v>
+        <v>38991</v>
       </c>
       <c r="C242" s="7">
-        <v>8984.77</v>
+        <v>8694.86</v>
       </c>
       <c r="D242" s="8">
-        <v>19545</v>
+        <v>18263.9</v>
       </c>
     </row>
     <row r="243" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B243" s="4">
-        <v>38777</v>
+        <v>38961</v>
       </c>
       <c r="C243" s="5">
-        <v>8059.4</v>
+        <v>8998.2</v>
       </c>
       <c r="D243" s="6">
-        <v>14671.8</v>
+        <v>18587.4</v>
       </c>
     </row>
     <row r="244" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B244" s="4">
-        <v>38749</v>
+        <v>38930</v>
       </c>
       <c r="C244" s="7">
-        <v>8038.04</v>
+        <v>9468.93</v>
       </c>
       <c r="D244" s="8">
-        <v>13456.3</v>
+        <v>18981.6</v>
       </c>
     </row>
     <row r="245" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B245" s="4">
-        <v>38718</v>
+        <v>38899</v>
       </c>
       <c r="C245" s="5">
-        <v>7925</v>
+        <v>9559</v>
       </c>
       <c r="D245" s="6">
-        <v>12982.5</v>
+        <v>17786.2</v>
       </c>
     </row>
     <row r="246" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B246" s="4">
-        <v>38687</v>
+        <v>38869</v>
       </c>
       <c r="C246" s="7">
-        <v>7585.93</v>
+        <v>8951.92</v>
       </c>
       <c r="D246" s="8">
-        <v>12692.22</v>
+        <v>16752.12</v>
       </c>
     </row>
     <row r="247" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B247" s="4">
-        <v>38657</v>
+        <v>38838</v>
       </c>
       <c r="C247" s="5">
-        <v>7167.5</v>
+        <v>9969.39</v>
       </c>
       <c r="D247" s="6">
-        <v>12049.76</v>
+        <v>20324.04</v>
       </c>
     </row>
     <row r="248" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B248" s="4">
-        <v>38626</v>
+        <v>38808</v>
       </c>
       <c r="C248" s="7">
-        <v>6873.8</v>
+        <v>8984.77</v>
       </c>
       <c r="D248" s="8">
-        <v>11595.4</v>
+        <v>19545</v>
       </c>
     </row>
     <row r="249" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B249" s="4">
-        <v>38596</v>
+        <v>38777</v>
       </c>
       <c r="C249" s="5">
-        <v>6534.6</v>
+        <v>8059.4</v>
       </c>
       <c r="D249" s="6">
-        <v>10855.6</v>
+        <v>14671.8</v>
       </c>
     </row>
     <row r="250" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B250" s="4">
-        <v>38565</v>
+        <v>38749</v>
       </c>
       <c r="C250" s="7">
-        <v>6249</v>
+        <v>8038.04</v>
       </c>
       <c r="D250" s="8">
-        <v>10704.8</v>
+        <v>13456.3</v>
       </c>
     </row>
     <row r="251" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B251" s="4">
-        <v>38534</v>
+        <v>38718</v>
       </c>
       <c r="C251" s="5">
-        <v>6058.26</v>
+        <v>7925</v>
       </c>
       <c r="D251" s="6">
-        <v>10655.65</v>
+        <v>12982.5</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B252" s="4">
-        <v>38504</v>
+        <v>38687</v>
       </c>
       <c r="C252" s="7">
-        <v>6134.23</v>
+        <v>7585.93</v>
       </c>
       <c r="D252" s="8">
-        <v>10912.88</v>
+        <v>12692.22</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B253" s="4">
-        <v>38473</v>
+        <v>38657</v>
       </c>
       <c r="C253" s="5">
-        <v>6030.38</v>
+        <v>7167.5</v>
       </c>
       <c r="D253" s="6">
-        <v>10639.81</v>
+        <v>12049.76</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B254" s="4">
-        <v>38443</v>
+        <v>38626</v>
       </c>
       <c r="C254" s="7">
-        <v>6150.58</v>
+        <v>6873.8</v>
       </c>
       <c r="D254" s="8">
-        <v>10729.04</v>
+        <v>11595.4</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B255" s="4">
-        <v>38412</v>
+        <v>38596</v>
       </c>
       <c r="C255" s="5">
-        <v>6262.2</v>
+        <v>6534.6</v>
       </c>
       <c r="D255" s="6">
-        <v>10820.6</v>
+        <v>10855.6</v>
       </c>
     </row>
     <row r="256" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B256" s="4">
-        <v>38384</v>
+        <v>38565</v>
       </c>
       <c r="C256" s="7">
-        <v>6107.5</v>
+        <v>6249</v>
       </c>
       <c r="D256" s="8">
-        <v>10732.5</v>
+        <v>10704.8</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B257" s="4">
-        <v>38353</v>
+        <v>38534</v>
       </c>
       <c r="C257" s="5">
-        <v>6148.6</v>
+        <v>6058.26</v>
       </c>
       <c r="D257" s="6">
-        <v>10436.92</v>
+        <v>10655.65</v>
       </c>
     </row>
     <row r="258" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B258" s="4">
-        <v>38322</v>
+        <v>38504</v>
       </c>
       <c r="C258" s="7">
-        <v>6444.62</v>
+        <v>6134.23</v>
       </c>
       <c r="D258" s="8">
-        <v>11143.65</v>
+        <v>10912.88</v>
       </c>
     </row>
     <row r="259" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B259" s="4">
-        <v>38292</v>
+        <v>38473</v>
       </c>
       <c r="C259" s="5">
-        <v>6550.83</v>
+        <v>6030.38</v>
       </c>
       <c r="D259" s="6">
-        <v>12000</v>
+        <v>10639.81</v>
       </c>
     </row>
     <row r="260" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B260" s="4">
-        <v>38261</v>
+        <v>38443</v>
       </c>
       <c r="C260" s="7">
-        <v>6360.83</v>
+        <v>6150.58</v>
       </c>
       <c r="D260" s="8">
-        <v>11408.54</v>
+        <v>10729.04</v>
       </c>
     </row>
     <row r="261" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B261" s="4">
-        <v>38231</v>
+        <v>38412</v>
       </c>
       <c r="C261" s="5">
-        <v>6170.43</v>
+        <v>6262.2</v>
       </c>
       <c r="D261" s="6">
-        <v>10521.96</v>
+        <v>10820.6</v>
       </c>
     </row>
     <row r="262" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B262" s="4">
-        <v>38200</v>
+        <v>38384</v>
       </c>
       <c r="C262" s="7">
-        <v>6125.8</v>
+        <v>6107.5</v>
       </c>
       <c r="D262" s="8">
-        <v>10861.6</v>
+        <v>10732.5</v>
       </c>
     </row>
     <row r="263" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B263" s="4">
-        <v>38169</v>
+        <v>38353</v>
       </c>
       <c r="C263" s="5">
-        <v>6059.42</v>
+        <v>6148.6</v>
       </c>
       <c r="D263" s="6">
-        <v>10200.77</v>
+        <v>10436.92</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B264" s="4">
-        <v>38139</v>
+        <v>38322</v>
       </c>
       <c r="C264" s="7">
-        <v>5862.12</v>
+        <v>6444.62</v>
       </c>
       <c r="D264" s="8">
-        <v>9491.73</v>
+        <v>11143.65</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B265" s="4">
-        <v>38108</v>
+        <v>38292</v>
       </c>
       <c r="C265" s="5">
-        <v>5736.46</v>
+        <v>6550.83</v>
       </c>
       <c r="D265" s="6">
-        <v>9468.96</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="266" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B266" s="4">
-        <v>38078</v>
+        <v>38261</v>
       </c>
       <c r="C266" s="7">
-        <v>5915.8</v>
+        <v>6360.83</v>
       </c>
       <c r="D266" s="8">
-        <v>11082.6</v>
+        <v>11408.54</v>
       </c>
     </row>
     <row r="267" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B267" s="4">
-        <v>38047</v>
+        <v>38231</v>
       </c>
       <c r="C267" s="5">
-        <v>5986.48</v>
+        <v>6170.43</v>
       </c>
       <c r="D267" s="6">
-        <v>11135.93</v>
+        <v>10521.96</v>
       </c>
     </row>
     <row r="268" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B268" s="4">
-        <v>38018</v>
+        <v>38200</v>
       </c>
       <c r="C268" s="7">
-        <v>6017.73</v>
+        <v>6125.8</v>
       </c>
       <c r="D268" s="8">
-        <v>10122.73</v>
+        <v>10861.6</v>
       </c>
     </row>
     <row r="269" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B269" s="4">
-        <v>37987</v>
+        <v>38169</v>
       </c>
       <c r="C269" s="5">
-        <v>6179.04</v>
+        <v>6059.42</v>
       </c>
       <c r="D269" s="6">
-        <v>9756.15</v>
+        <v>10200.77</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B270" s="4">
-        <v>37956</v>
+        <v>38139</v>
       </c>
       <c r="C270" s="7">
-        <v>6094.07</v>
+        <v>5862.12</v>
       </c>
       <c r="D270" s="8">
-        <v>9074</v>
+        <v>9491.73</v>
       </c>
     </row>
     <row r="271" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B271" s="4">
-        <v>37926</v>
+        <v>38108</v>
       </c>
       <c r="C271" s="5">
-        <v>5850</v>
+        <v>5736.46</v>
       </c>
       <c r="D271" s="6">
-        <v>8423</v>
+        <v>9468.96</v>
       </c>
     </row>
     <row r="272" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B272" s="4">
-        <v>37895</v>
+        <v>38078</v>
       </c>
       <c r="C272" s="7">
-        <v>5695.19</v>
+        <v>5915.8</v>
       </c>
       <c r="D272" s="8">
-        <v>8207</v>
+        <v>11082.6</v>
       </c>
     </row>
     <row r="273" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B273" s="4">
-        <v>37865</v>
+        <v>38047</v>
       </c>
       <c r="C273" s="5">
-        <v>5718.4</v>
+        <v>5986.48</v>
       </c>
       <c r="D273" s="6">
-        <v>8462</v>
+        <v>11135.93</v>
       </c>
     </row>
     <row r="274" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B274" s="4">
-        <v>37834</v>
+        <v>38018</v>
       </c>
       <c r="C274" s="7">
-        <v>5462.17</v>
+        <v>6017.73</v>
       </c>
       <c r="D274" s="8">
-        <v>8167</v>
+        <v>10122.73</v>
       </c>
     </row>
     <row r="275" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B275" s="4">
-        <v>37803</v>
+        <v>37987</v>
       </c>
       <c r="C275" s="5">
-        <v>5362.5</v>
+        <v>6179.04</v>
       </c>
       <c r="D275" s="6">
-        <v>7852</v>
+        <v>9756.15</v>
       </c>
     </row>
     <row r="276" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B276" s="4">
-        <v>37773</v>
+        <v>37956</v>
       </c>
       <c r="C276" s="7">
-        <v>5509.4</v>
+        <v>6094.07</v>
       </c>
       <c r="D276" s="8">
-        <v>7659</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="277" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B277" s="4">
-        <v>37742</v>
+        <v>37926</v>
       </c>
       <c r="C277" s="5">
-        <v>5560.77</v>
+        <v>5850</v>
       </c>
       <c r="D277" s="6">
-        <v>8006.54</v>
+        <v>8423</v>
       </c>
     </row>
     <row r="278" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B278" s="4">
-        <v>37712</v>
+        <v>37895</v>
       </c>
       <c r="C278" s="7">
-        <v>5191.6</v>
+        <v>5695.19</v>
       </c>
       <c r="D278" s="8">
-        <v>7797.4</v>
+        <v>8207</v>
       </c>
     </row>
     <row r="279" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B279" s="4">
-        <v>37681</v>
+        <v>37865</v>
       </c>
       <c r="C279" s="5">
-        <v>5432.71</v>
+        <v>5718.4</v>
       </c>
       <c r="D279" s="6">
-        <v>7803.75</v>
+        <v>8462</v>
       </c>
     </row>
     <row r="280" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B280" s="4">
-        <v>37653</v>
+        <v>37834</v>
       </c>
       <c r="C280" s="7">
-        <v>5771.3</v>
+        <v>5462.17</v>
       </c>
       <c r="D280" s="8">
-        <v>7952.27</v>
+        <v>8167</v>
       </c>
     </row>
     <row r="281" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B281" s="4">
-        <v>37622</v>
+        <v>37803</v>
       </c>
       <c r="C281" s="5">
-        <v>5752.04</v>
+        <v>5362.5</v>
       </c>
       <c r="D281" s="6">
-        <v>8156.48</v>
+        <v>7852</v>
       </c>
     </row>
     <row r="282" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B282" s="4">
-        <v>37591</v>
+        <v>37773</v>
       </c>
       <c r="C282" s="7">
-        <v>5443.6</v>
+        <v>5509.4</v>
       </c>
       <c r="D282" s="8">
-        <v>7932.6</v>
+        <v>7659</v>
       </c>
     </row>
     <row r="283" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B283" s="4">
-        <v>37561</v>
+        <v>37742</v>
       </c>
       <c r="C283" s="5">
-        <v>5242.92</v>
+        <v>5560.77</v>
       </c>
       <c r="D283" s="6">
-        <v>7824.38</v>
+        <v>8006.54</v>
       </c>
     </row>
     <row r="284" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B284" s="4">
-        <v>37530</v>
+        <v>37712</v>
       </c>
       <c r="C284" s="7">
-        <v>5210.4</v>
+        <v>5191.6</v>
       </c>
       <c r="D284" s="8">
-        <v>7733.8</v>
+        <v>7797.4</v>
       </c>
     </row>
     <row r="285" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B285" s="4">
-        <v>37500</v>
+        <v>37681</v>
       </c>
       <c r="C285" s="5">
-        <v>5239.05</v>
+        <v>5432.71</v>
       </c>
       <c r="D285" s="6">
-        <v>7879.76</v>
+        <v>7803.75</v>
       </c>
     </row>
     <row r="286" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B286" s="4">
-        <v>37469</v>
+        <v>37653</v>
       </c>
       <c r="C286" s="7">
-        <v>5129.2</v>
+        <v>5771.3</v>
       </c>
       <c r="D286" s="8">
-        <v>7882.8</v>
+        <v>7952.27</v>
       </c>
     </row>
     <row r="287" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B287" s="4">
-        <v>37438</v>
+        <v>37622</v>
       </c>
       <c r="C287" s="5">
-        <v>5187.5</v>
+        <v>5752.04</v>
       </c>
       <c r="D287" s="6">
-        <v>8358.27</v>
+        <v>8156.48</v>
       </c>
     </row>
     <row r="288" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B288" s="4">
-        <v>37408</v>
+        <v>37591</v>
       </c>
       <c r="C288" s="7">
-        <v>5313.2</v>
+        <v>5443.6</v>
       </c>
       <c r="D288" s="8">
-        <v>8342.6</v>
+        <v>7932.6</v>
       </c>
     </row>
     <row r="289" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B289" s="4">
-        <v>37377</v>
+        <v>37561</v>
       </c>
       <c r="C289" s="5">
-        <v>5225.8</v>
+        <v>5242.92</v>
       </c>
       <c r="D289" s="6">
-        <v>8146.8</v>
+        <v>7824.38</v>
       </c>
     </row>
     <row r="290" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B290" s="4">
-        <v>37347</v>
+        <v>37530</v>
       </c>
       <c r="C290" s="7">
-        <v>5040.63</v>
+        <v>5210.4</v>
       </c>
       <c r="D290" s="8">
-        <v>7872.83</v>
+        <v>7733.8</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B291" s="4">
-        <v>37316</v>
+        <v>37500</v>
       </c>
       <c r="C291" s="5">
-        <v>4920.21</v>
+        <v>5239.05</v>
       </c>
       <c r="D291" s="6">
-        <v>7808.26</v>
+        <v>7879.76</v>
       </c>
     </row>
     <row r="292" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B292" s="4">
-        <v>37288</v>
+        <v>37469</v>
       </c>
       <c r="C292" s="7">
-        <v>4901.04</v>
+        <v>5129.2</v>
       </c>
       <c r="D292" s="8">
-        <v>7625.21</v>
+        <v>7882.8</v>
       </c>
     </row>
     <row r="293" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B293" s="4">
-        <v>37257</v>
+        <v>37438</v>
       </c>
       <c r="C293" s="5">
-        <v>4692.69</v>
+        <v>5187.5</v>
       </c>
       <c r="D293" s="6">
-        <v>7683.85</v>
+        <v>8358.27</v>
       </c>
     </row>
     <row r="294" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B294" s="4">
-        <v>37226</v>
+        <v>37408</v>
       </c>
       <c r="C294" s="7">
-        <v>4576.46</v>
+        <v>5313.2</v>
       </c>
       <c r="D294" s="8">
-        <v>7415.2</v>
+        <v>8342.6</v>
       </c>
     </row>
     <row r="295" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B295" s="4">
-        <v>37196</v>
+        <v>37377</v>
       </c>
       <c r="C295" s="5">
-        <v>4603.96</v>
+        <v>5225.8</v>
       </c>
       <c r="D295" s="6">
-        <v>7191.4</v>
+        <v>8146.8</v>
       </c>
     </row>
     <row r="296" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B296" s="4">
-        <v>37165</v>
+        <v>37347</v>
       </c>
       <c r="C296" s="7">
-        <v>4687.6</v>
+        <v>5040.63</v>
       </c>
       <c r="D296" s="8">
-        <v>7574.79</v>
+        <v>7872.83</v>
       </c>
     </row>
     <row r="297" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B297" s="4">
-        <v>37135</v>
+        <v>37316</v>
       </c>
       <c r="C297" s="5">
-        <v>4631.3</v>
+        <v>4920.21</v>
       </c>
       <c r="D297" s="6">
-        <v>7399.35</v>
+        <v>7808.26</v>
       </c>
     </row>
     <row r="298" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B298" s="4">
-        <v>37104</v>
+        <v>37288</v>
       </c>
       <c r="C298" s="7">
-        <v>4448.64</v>
+        <v>4901.04</v>
       </c>
       <c r="D298" s="8">
-        <v>7166.43</v>
+        <v>7625.21</v>
       </c>
     </row>
     <row r="299" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B299" s="4">
-        <v>37073</v>
+        <v>37257</v>
       </c>
       <c r="C299" s="5">
-        <v>4379.58</v>
+        <v>4692.69</v>
       </c>
       <c r="D299" s="6">
-        <v>7258.13</v>
+        <v>7683.85</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B300" s="4">
-        <v>37043</v>
+        <v>37226</v>
       </c>
       <c r="C300" s="7">
-        <v>4400.2</v>
+        <v>4576.46</v>
       </c>
       <c r="D300" s="8">
-        <v>7413.96</v>
+        <v>7415.2</v>
       </c>
     </row>
     <row r="301" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B301" s="4">
-        <v>37012</v>
+        <v>37196</v>
       </c>
       <c r="C301" s="5">
-        <v>4440.58</v>
+        <v>4603.96</v>
       </c>
       <c r="D301" s="6">
-        <v>7466.73</v>
+        <v>7191.4</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B302" s="4">
-        <v>36982</v>
+        <v>37165</v>
       </c>
       <c r="C302" s="7">
-        <v>4267.17</v>
+        <v>4687.6</v>
       </c>
       <c r="D302" s="8">
-        <v>7363</v>
+        <v>7574.79</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B303" s="4">
-        <v>36951</v>
+        <v>37135</v>
       </c>
       <c r="C303" s="5">
-        <v>4268.6</v>
+        <v>4631.3</v>
       </c>
       <c r="D303" s="6">
-        <v>7364</v>
+        <v>7399.35</v>
       </c>
     </row>
     <row r="304" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B304" s="4">
-        <v>36923</v>
+        <v>37104</v>
       </c>
       <c r="C304" s="7">
-        <v>4369.57</v>
+        <v>4448.64</v>
       </c>
       <c r="D304" s="8">
-        <v>7621.52</v>
+        <v>7166.43</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B305" s="4">
-        <v>36892</v>
+        <v>37073</v>
       </c>
       <c r="C305" s="5">
-        <v>4465.58</v>
+        <v>4379.58</v>
       </c>
       <c r="D305" s="6">
-        <v>7753.46</v>
+        <v>7258.13</v>
       </c>
     </row>
     <row r="306" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B306" s="4">
-        <v>36861</v>
+        <v>37043</v>
       </c>
       <c r="C306" s="7">
-        <v>4540.8</v>
+        <v>4400.2</v>
       </c>
       <c r="D306" s="8">
-        <v>7798.2</v>
+        <v>7413.96</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B307" s="4">
-        <v>36831</v>
+        <v>37012</v>
       </c>
       <c r="C307" s="5">
-        <v>4482.69</v>
+        <v>4440.58</v>
       </c>
       <c r="D307" s="6">
-        <v>7891.15</v>
+        <v>7466.73</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B308" s="4">
-        <v>36800</v>
+        <v>36982</v>
       </c>
       <c r="C308" s="7">
-        <v>4537.61</v>
+        <v>4267.17</v>
       </c>
       <c r="D308" s="8">
-        <v>8076.96</v>
+        <v>7363</v>
       </c>
     </row>
     <row r="309" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B309" s="4">
-        <v>36770</v>
+        <v>36951</v>
       </c>
       <c r="C309" s="5">
-        <v>4518.13</v>
+        <v>4268.6</v>
       </c>
       <c r="D309" s="6">
-        <v>8062.29</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="310" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B310" s="4">
-        <v>36739</v>
+        <v>36923</v>
       </c>
       <c r="C310" s="7">
-        <v>4516.25</v>
+        <v>4369.57</v>
       </c>
       <c r="D310" s="8">
-        <v>8014.17</v>
+        <v>7621.52</v>
       </c>
     </row>
     <row r="311" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B311" s="4">
-        <v>36708</v>
+        <v>36892</v>
       </c>
       <c r="C311" s="5">
-        <v>4529.2</v>
+        <v>4465.58</v>
       </c>
       <c r="D311" s="6">
-        <v>7990</v>
+        <v>7753.46</v>
       </c>
     </row>
     <row r="312" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B312" s="4">
-        <v>36678</v>
+        <v>36861</v>
       </c>
       <c r="C312" s="7">
-        <v>4521.15</v>
+        <v>4540.8</v>
       </c>
       <c r="D312" s="8">
-        <v>7958.46</v>
+        <v>7798.2</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B313" s="4">
-        <v>36647</v>
+        <v>36831</v>
       </c>
       <c r="C313" s="5">
-        <v>4473.6</v>
+        <v>4482.69</v>
       </c>
       <c r="D313" s="6">
-        <v>7868.39</v>
+        <v>7891.15</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B314" s="4">
-        <v>36617</v>
+        <v>36800</v>
       </c>
       <c r="C314" s="7">
-        <v>4460</v>
+        <v>4537.61</v>
       </c>
       <c r="D314" s="8">
-        <v>8022.08</v>
+        <v>8076.96</v>
       </c>
     </row>
     <row r="315" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B315" s="4">
-        <v>36586</v>
+        <v>36770</v>
       </c>
       <c r="C315" s="5">
-        <v>4541.6</v>
+        <v>4518.13</v>
       </c>
       <c r="D315" s="6">
-        <v>8003.8</v>
+        <v>8062.29</v>
       </c>
     </row>
     <row r="316" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B316" s="4">
-        <v>36557</v>
+        <v>36739</v>
       </c>
       <c r="C316" s="7">
-        <v>4706.74</v>
+        <v>4516.25</v>
       </c>
       <c r="D316" s="8">
-        <v>8191.74</v>
+        <v>8014.17</v>
       </c>
     </row>
     <row r="317" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B317" s="4">
-        <v>36526</v>
+        <v>36708</v>
       </c>
       <c r="C317" s="5">
-        <v>4508.91</v>
+        <v>4529.2</v>
       </c>
       <c r="D317" s="6">
-        <v>8123.7</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="318" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B318" s="4">
-        <v>36495</v>
+        <v>36678</v>
       </c>
       <c r="C318" s="7">
-        <v>4473</v>
+        <v>4521.15</v>
       </c>
       <c r="D318" s="8">
-        <v>8102.2</v>
+        <v>7958.46</v>
       </c>
     </row>
     <row r="319" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B319" s="4">
-        <v>36465</v>
+        <v>36647</v>
       </c>
       <c r="C319" s="5">
-        <v>4615.24</v>
+        <v>4473.6</v>
       </c>
       <c r="D319" s="6">
-        <v>8112.86</v>
+        <v>7868.39</v>
       </c>
     </row>
     <row r="320" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B320" s="4">
-        <v>36434</v>
+        <v>36617</v>
       </c>
       <c r="C320" s="7">
-        <v>4748.96</v>
+        <v>4460</v>
       </c>
       <c r="D320" s="8">
-        <v>8326.25</v>
+        <v>8022.08</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B321" s="4">
-        <v>36404</v>
+        <v>36586</v>
       </c>
       <c r="C321" s="5">
-        <v>4178.57</v>
+        <v>4541.6</v>
       </c>
       <c r="D321" s="6">
-        <v>8107.62</v>
+        <v>8003.8</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B322" s="4">
-        <v>36373</v>
+        <v>36557</v>
       </c>
       <c r="C322" s="7">
-        <v>4086.6</v>
+        <v>4706.74</v>
       </c>
       <c r="D322" s="8">
-        <v>8142.8</v>
+        <v>8191.74</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B323" s="4">
-        <v>36342</v>
+        <v>36526</v>
       </c>
       <c r="C323" s="5">
-        <v>4051.4</v>
+        <v>4508.91</v>
       </c>
       <c r="D323" s="6">
-        <v>8007.4</v>
+        <v>8123.7</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B324" s="4">
-        <v>36312</v>
+        <v>36495</v>
       </c>
       <c r="C324" s="7">
-        <v>4108.65</v>
+        <v>4473</v>
       </c>
       <c r="D324" s="8">
-        <v>7796.54</v>
+        <v>8102.2</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B325" s="4">
-        <v>36281</v>
+        <v>36465</v>
       </c>
       <c r="C325" s="5">
-        <v>4313.6</v>
+        <v>4615.24</v>
       </c>
       <c r="D325" s="6">
-        <v>8095</v>
+        <v>8112.86</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B326" s="4">
-        <v>36251</v>
+        <v>36434</v>
       </c>
       <c r="C326" s="7">
-        <v>4389.4</v>
+        <v>4748.96</v>
       </c>
       <c r="D326" s="8">
-        <v>7793.4</v>
+        <v>8326.25</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B327" s="4">
-        <v>36220</v>
+        <v>36404</v>
       </c>
       <c r="C327" s="5">
-        <v>4330</v>
+        <v>4178.57</v>
       </c>
       <c r="D327" s="6">
-        <v>7827</v>
+        <v>8107.62</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B328" s="4">
-        <v>36192</v>
+        <v>36373</v>
       </c>
       <c r="C328" s="7">
-        <v>4357</v>
+        <v>4086.6</v>
       </c>
       <c r="D328" s="8">
-        <v>8223</v>
+        <v>8142.8</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B329" s="4">
-        <v>36161</v>
+        <v>36342</v>
       </c>
       <c r="C329" s="5">
-        <v>4347</v>
+        <v>4051.4</v>
       </c>
       <c r="D329" s="6">
-        <v>7715</v>
+        <v>8007.4</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B330" s="4">
-        <v>36130</v>
+        <v>36312</v>
       </c>
       <c r="C330" s="7">
-        <v>4280</v>
+        <v>4108.65</v>
       </c>
       <c r="D330" s="8">
-        <v>7360</v>
+        <v>7796.54</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B331" s="4">
-        <v>36100</v>
+        <v>36281</v>
       </c>
       <c r="C331" s="5">
-        <v>4306</v>
+        <v>4313.6</v>
       </c>
       <c r="D331" s="6">
-        <v>7499</v>
+        <v>8095</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B332" s="4">
-        <v>36069</v>
+        <v>36251</v>
       </c>
       <c r="C332" s="7">
-        <v>4336</v>
+        <v>4389.4</v>
       </c>
       <c r="D332" s="8">
-        <v>7528</v>
+        <v>7793.4</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B333" s="4">
-        <v>36039</v>
+        <v>36220</v>
       </c>
       <c r="C333" s="5">
-        <v>4234</v>
+        <v>4330</v>
       </c>
       <c r="D333" s="6">
-        <v>7560</v>
+        <v>7827</v>
       </c>
     </row>
     <row r="334" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B334" s="4">
-        <v>36008</v>
+        <v>36192</v>
       </c>
       <c r="C334" s="7">
-        <v>4189</v>
+        <v>4357</v>
       </c>
       <c r="D334" s="8">
-        <v>7864</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B335" s="4">
-        <v>35977</v>
+        <v>36161</v>
       </c>
       <c r="C335" s="5">
-        <v>4271</v>
+        <v>4347</v>
       </c>
       <c r="D335" s="6">
-        <v>8124</v>
+        <v>7715</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B336" s="4">
-        <v>35947</v>
+        <v>36130</v>
       </c>
       <c r="C336" s="7">
-        <v>4215</v>
+        <v>4280</v>
       </c>
       <c r="D336" s="8">
-        <v>7765</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B337" s="4">
-        <v>35916</v>
+        <v>36100</v>
       </c>
       <c r="C337" s="5">
-        <v>4143</v>
+        <v>4306</v>
       </c>
       <c r="D337" s="6">
-        <v>7989</v>
+        <v>7499</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B338" s="4">
-        <v>35886</v>
+        <v>36069</v>
       </c>
       <c r="C338" s="7">
-        <v>4210</v>
+        <v>4336</v>
       </c>
       <c r="D338" s="8">
-        <v>8810</v>
+        <v>7528</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B339" s="4">
-        <v>35855</v>
+        <v>36039</v>
       </c>
       <c r="C339" s="5">
-        <v>3995.43</v>
+        <v>4234</v>
       </c>
       <c r="D339" s="6">
-        <v>8577.61</v>
+        <v>7560</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B340" s="4">
-        <v>35827</v>
+        <v>36008</v>
       </c>
       <c r="C340" s="7">
-        <v>3995</v>
+        <v>4189</v>
       </c>
       <c r="D340" s="8">
-        <v>8829.32</v>
+        <v>7864</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B341" s="4">
-        <v>35796</v>
+        <v>35977</v>
       </c>
       <c r="C341" s="5">
-        <v>4008.54</v>
+        <v>4271</v>
       </c>
       <c r="D341" s="6">
-        <v>8285.63</v>
+        <v>8124</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B342" s="4">
-        <v>35765</v>
+        <v>35947</v>
       </c>
       <c r="C342" s="7">
-        <v>3995</v>
+        <v>4215</v>
       </c>
       <c r="D342" s="8">
-        <v>8068.96</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B343" s="4">
-        <v>35735</v>
+        <v>35916</v>
       </c>
       <c r="C343" s="5">
-        <v>4135.68</v>
+        <v>4143</v>
       </c>
       <c r="D343" s="6">
-        <v>7020.91</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="344" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B344" s="4">
-        <v>35704</v>
+        <v>35886</v>
       </c>
       <c r="C344" s="7">
-        <v>4399.6</v>
+        <v>4210</v>
       </c>
       <c r="D344" s="8">
-        <v>7084.4</v>
+        <v>8810</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B345" s="4">
-        <v>35674</v>
+        <v>35855</v>
       </c>
       <c r="C345" s="5">
-        <v>4441.52</v>
+        <v>3995.43</v>
       </c>
       <c r="D345" s="6">
-        <v>6857.83</v>
+        <v>8577.61</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B346" s="4">
-        <v>35643</v>
+        <v>35827</v>
       </c>
       <c r="C346" s="7">
-        <v>4511.5</v>
+        <v>3995</v>
       </c>
       <c r="D346" s="8">
-        <v>6511.25</v>
+        <v>8829.32</v>
       </c>
     </row>
     <row r="347" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B347" s="4">
-        <v>35612</v>
+        <v>35796</v>
       </c>
       <c r="C347" s="5">
-        <v>4468.8</v>
+        <v>4008.54</v>
       </c>
       <c r="D347" s="6">
-        <v>6332.2</v>
+        <v>8285.63</v>
       </c>
     </row>
     <row r="348" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B348" s="4">
-        <v>35582</v>
+        <v>35765</v>
       </c>
       <c r="C348" s="7">
-        <v>4640.6</v>
+        <v>3995</v>
       </c>
       <c r="D348" s="8">
-        <v>6770.4</v>
+        <v>8068.96</v>
       </c>
     </row>
     <row r="349" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B349" s="4">
-        <v>35551</v>
+        <v>35735</v>
       </c>
       <c r="C349" s="5">
-        <v>4784.8</v>
+        <v>4135.68</v>
       </c>
       <c r="D349" s="6">
-        <v>6919.4</v>
+        <v>7020.91</v>
       </c>
     </row>
     <row r="350" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B350" s="4">
-        <v>35521</v>
+        <v>35704</v>
       </c>
       <c r="C350" s="7">
-        <v>4788.33</v>
+        <v>4399.6</v>
       </c>
       <c r="D350" s="8">
-        <v>6969.38</v>
+        <v>7084.4</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B351" s="4">
-        <v>35490</v>
+        <v>35674</v>
       </c>
       <c r="C351" s="5">
-        <v>4788.7</v>
+        <v>4441.52</v>
       </c>
       <c r="D351" s="6">
-        <v>7421.09</v>
+        <v>6857.83</v>
       </c>
     </row>
     <row r="352" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B352" s="4">
-        <v>35462</v>
+        <v>35643</v>
       </c>
       <c r="C352" s="7">
-        <v>4826.04</v>
+        <v>4511.5</v>
       </c>
       <c r="D352" s="8">
-        <v>7307.29</v>
+        <v>6511.25</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B353" s="4">
-        <v>35431</v>
+        <v>35612</v>
       </c>
       <c r="C353" s="5">
-        <v>4896.04</v>
+        <v>4468.8</v>
       </c>
       <c r="D353" s="6">
-        <v>6851.88</v>
+        <v>6332.2</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B354" s="4">
-        <v>35400</v>
+        <v>35582</v>
       </c>
       <c r="C354" s="7">
-        <v>5030.4</v>
+        <v>4640.6</v>
       </c>
       <c r="D354" s="8">
-        <v>6871.2</v>
+        <v>6770.4</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B355" s="4">
-        <v>35370</v>
+        <v>35551</v>
       </c>
       <c r="C355" s="5">
-        <v>5139.78</v>
+        <v>4784.8</v>
       </c>
       <c r="D355" s="6">
-        <v>6919.35</v>
+        <v>6919.4</v>
       </c>
     </row>
     <row r="356" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B356" s="4">
-        <v>35339</v>
+        <v>35521</v>
       </c>
       <c r="C356" s="7">
-        <v>5136.8</v>
+        <v>4788.33</v>
       </c>
       <c r="D356" s="8">
-        <v>6974.4</v>
+        <v>6969.38</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B357" s="4">
-        <v>35309</v>
+        <v>35490</v>
       </c>
       <c r="C357" s="5">
-        <v>5133.25</v>
+        <v>4788.7</v>
       </c>
       <c r="D357" s="6">
-        <v>7108</v>
+        <v>7421.09</v>
       </c>
     </row>
     <row r="358" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B358" s="4">
-        <v>35278</v>
+        <v>35462</v>
       </c>
       <c r="C358" s="7">
-        <v>5166.67</v>
+        <v>4826.04</v>
       </c>
       <c r="D358" s="8">
-        <v>7192.08</v>
+        <v>7307.29</v>
       </c>
     </row>
     <row r="359" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B359" s="4">
-        <v>35247</v>
+        <v>35431</v>
       </c>
       <c r="C359" s="5">
-        <v>5114.19</v>
+        <v>4896.04</v>
       </c>
       <c r="D359" s="6">
-        <v>7104.5</v>
+        <v>6851.88</v>
       </c>
     </row>
     <row r="360" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B360" s="4">
-        <v>35217</v>
+        <v>35400</v>
       </c>
       <c r="C360" s="7">
-        <v>5110.8</v>
+        <v>5030.4</v>
       </c>
       <c r="D360" s="8">
-        <v>7211.72</v>
+        <v>6871.2</v>
       </c>
     </row>
     <row r="361" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B361" s="4">
-        <v>35186</v>
+        <v>35370</v>
       </c>
       <c r="C361" s="5">
-        <v>5286</v>
+        <v>5139.78</v>
       </c>
       <c r="D361" s="6">
-        <v>7551.72</v>
+        <v>6919.35</v>
       </c>
     </row>
     <row r="362" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B362" s="4">
-        <v>35156</v>
+        <v>35339</v>
       </c>
       <c r="C362" s="7">
-        <v>5219.87</v>
+        <v>5136.8</v>
       </c>
       <c r="D362" s="8">
-        <v>7467.61</v>
+        <v>6974.4</v>
       </c>
     </row>
     <row r="363" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B363" s="4">
-        <v>35125</v>
+        <v>35309</v>
       </c>
       <c r="C363" s="5">
-        <v>5199.55</v>
+        <v>5133.25</v>
       </c>
       <c r="D363" s="6">
-        <v>7471.5</v>
+        <v>7108</v>
       </c>
     </row>
     <row r="364" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B364" s="4">
-        <v>35096</v>
+        <v>35278</v>
       </c>
       <c r="C364" s="7">
-        <v>5452.96</v>
+        <v>5166.67</v>
       </c>
       <c r="D364" s="8">
-        <v>7964.17</v>
+        <v>7192.08</v>
       </c>
     </row>
     <row r="365" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B365" s="4">
-        <v>35065</v>
+        <v>35247</v>
       </c>
       <c r="C365" s="5">
-        <v>5301.2</v>
+        <v>5114.19</v>
       </c>
       <c r="D365" s="6">
-        <v>7655.88</v>
+        <v>7104.5</v>
       </c>
     </row>
     <row r="366" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B366" s="4">
-        <v>35034</v>
+        <v>35217</v>
       </c>
       <c r="C366" s="7">
-        <v>5058.08</v>
+        <v>5110.8</v>
       </c>
       <c r="D366" s="8">
-        <v>7205.25</v>
+        <v>7211.72</v>
       </c>
     </row>
     <row r="367" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B367" s="4">
-        <v>35004</v>
+        <v>35186</v>
       </c>
       <c r="C367" s="5">
-        <v>5038.58</v>
+        <v>5286</v>
       </c>
       <c r="D367" s="6">
-        <v>7353.42</v>
+        <v>7551.72</v>
       </c>
     </row>
     <row r="368" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B368" s="4">
-        <v>34973</v>
+        <v>35156</v>
       </c>
       <c r="C368" s="7">
-        <v>4956.06</v>
+        <v>5219.87</v>
       </c>
       <c r="D368" s="8">
-        <v>7511.71</v>
+        <v>7467.61</v>
       </c>
     </row>
     <row r="369" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B369" s="4">
-        <v>34943</v>
+        <v>35125</v>
       </c>
       <c r="C369" s="5">
-        <v>4777.26</v>
+        <v>5199.55</v>
       </c>
       <c r="D369" s="6">
-        <v>7188.17</v>
+        <v>7471.5</v>
       </c>
     </row>
     <row r="370" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B370" s="4">
-        <v>34912</v>
+        <v>35096</v>
       </c>
       <c r="C370" s="7">
-        <v>4687.05</v>
+        <v>5452.96</v>
       </c>
       <c r="D370" s="8">
-        <v>6816.43</v>
+        <v>7964.17</v>
       </c>
     </row>
     <row r="371" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B371" s="4">
-        <v>34881</v>
+        <v>35065</v>
       </c>
       <c r="C371" s="5">
-        <v>4689.15</v>
+        <v>5301.2</v>
       </c>
       <c r="D371" s="6">
-        <v>6683.54</v>
+        <v>7655.88</v>
       </c>
     </row>
     <row r="372" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B372" s="4">
-        <v>34851</v>
+        <v>35034</v>
       </c>
       <c r="C372" s="7">
-        <v>4731.27</v>
+        <v>5058.08</v>
       </c>
       <c r="D372" s="8">
-        <v>6793.77</v>
+        <v>7205.25</v>
       </c>
     </row>
     <row r="373" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B373" s="4">
-        <v>34820</v>
+        <v>35004</v>
       </c>
       <c r="C373" s="5">
-        <v>4795.19</v>
+        <v>5038.58</v>
       </c>
       <c r="D373" s="6">
-        <v>7105.81</v>
+        <v>7353.42</v>
       </c>
     </row>
     <row r="374" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B374" s="4">
-        <v>34790</v>
+        <v>34973</v>
       </c>
       <c r="C374" s="7">
-        <v>4804.9</v>
+        <v>4956.06</v>
       </c>
       <c r="D374" s="8">
-        <v>6896.38</v>
+        <v>7511.71</v>
       </c>
     </row>
     <row r="375" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B375" s="4">
-        <v>34759</v>
+        <v>34943</v>
       </c>
       <c r="C375" s="5">
-        <v>4660.65</v>
+        <v>4777.26</v>
       </c>
       <c r="D375" s="6">
-        <v>6188.96</v>
+        <v>7188.17</v>
       </c>
     </row>
     <row r="376" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B376" s="4">
-        <v>34731</v>
+        <v>34912</v>
       </c>
       <c r="C376" s="7">
-        <v>4681.64</v>
+        <v>4687.05</v>
       </c>
       <c r="D376" s="8">
-        <v>6259.95</v>
+        <v>6816.43</v>
       </c>
     </row>
     <row r="377" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B377" s="4">
-        <v>34700</v>
+        <v>34881</v>
       </c>
       <c r="C377" s="5">
-        <v>4700.83</v>
+        <v>4689.15</v>
       </c>
       <c r="D377" s="6">
-        <v>6361.04</v>
+        <v>6683.54</v>
       </c>
     </row>
     <row r="378" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B378" s="4">
-        <v>34669</v>
+        <v>34851</v>
       </c>
       <c r="C378" s="7">
-        <v>4677.7</v>
+        <v>4731.27</v>
       </c>
       <c r="D378" s="8">
-        <v>6430.85</v>
+        <v>6793.77</v>
       </c>
     </row>
     <row r="379" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B379" s="4">
-        <v>34639</v>
+        <v>34820</v>
       </c>
       <c r="C379" s="5">
-        <v>4748.48</v>
+        <v>4795.19</v>
       </c>
       <c r="D379" s="6">
-        <v>6866.38</v>
+        <v>7105.81</v>
       </c>
     </row>
     <row r="380" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B380" s="4">
-        <v>34608</v>
+        <v>34790</v>
       </c>
       <c r="C380" s="7">
-        <v>4755.16</v>
+        <v>4804.9</v>
       </c>
       <c r="D380" s="8">
-        <v>7054.56</v>
+        <v>6896.38</v>
       </c>
     </row>
     <row r="381" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B381" s="4">
-        <v>34578</v>
+        <v>34759</v>
       </c>
       <c r="C381" s="5">
-        <v>4682.17</v>
+        <v>4660.65</v>
       </c>
       <c r="D381" s="6">
-        <v>6965.29</v>
+        <v>6188.96</v>
       </c>
     </row>
     <row r="382" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B382" s="4">
-        <v>34547</v>
+        <v>34731</v>
       </c>
       <c r="C382" s="7">
-        <v>4602.83</v>
+        <v>4681.64</v>
       </c>
       <c r="D382" s="8">
-        <v>6661.22</v>
+        <v>6259.95</v>
       </c>
     </row>
     <row r="383" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B383" s="4">
-        <v>34516</v>
+        <v>34700</v>
       </c>
       <c r="C383" s="5">
-        <v>4597.42</v>
+        <v>4700.83</v>
       </c>
       <c r="D383" s="6">
-        <v>6707.35</v>
+        <v>6361.04</v>
       </c>
     </row>
     <row r="384" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B384" s="4">
-        <v>34486</v>
+        <v>34669</v>
       </c>
       <c r="C384" s="7">
-        <v>4593.58</v>
+        <v>4677.7</v>
       </c>
       <c r="D384" s="8">
-        <v>6784.88</v>
+        <v>6430.85</v>
       </c>
     </row>
     <row r="385" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B385" s="4">
-        <v>34455</v>
+        <v>34639</v>
       </c>
       <c r="C385" s="5">
-        <v>4665.38</v>
+        <v>4748.48</v>
       </c>
       <c r="D385" s="6">
-        <v>6980.96</v>
+        <v>6866.38</v>
       </c>
     </row>
     <row r="386" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B386" s="4">
-        <v>34425</v>
+        <v>34608</v>
       </c>
       <c r="C386" s="7">
-        <v>4641.04</v>
+        <v>4755.16</v>
       </c>
       <c r="D386" s="8">
-        <v>7046.25</v>
+        <v>7054.56</v>
       </c>
     </row>
     <row r="387" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B387" s="4">
-        <v>34394</v>
+        <v>34578</v>
       </c>
       <c r="C387" s="5">
-        <v>4598.19</v>
+        <v>4682.17</v>
       </c>
       <c r="D387" s="6">
-        <v>7062.58</v>
+        <v>6965.29</v>
       </c>
     </row>
     <row r="388" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B388" s="4">
-        <v>34366</v>
+        <v>34547</v>
       </c>
       <c r="C388" s="7">
-        <v>4606.21</v>
+        <v>4602.83</v>
       </c>
       <c r="D388" s="8">
-        <v>6839.5</v>
+        <v>6661.22</v>
       </c>
     </row>
     <row r="389" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B389" s="4">
-        <v>34335</v>
+        <v>34516</v>
       </c>
       <c r="C389" s="5">
-        <v>4659.04</v>
+        <v>4597.42</v>
       </c>
       <c r="D389" s="6">
-        <v>6746</v>
+        <v>6707.35</v>
       </c>
     </row>
     <row r="390" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B390" s="4">
-        <v>34304</v>
+        <v>34486</v>
       </c>
       <c r="C390" s="7">
-        <v>4637.46</v>
+        <v>4593.58</v>
       </c>
       <c r="D390" s="8">
-        <v>6562.65</v>
+        <v>6784.88</v>
       </c>
     </row>
     <row r="391" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B391" s="4">
-        <v>34274</v>
+        <v>34455</v>
       </c>
       <c r="C391" s="5">
-        <v>4587.09</v>
+        <v>4665.38</v>
       </c>
       <c r="D391" s="6">
-        <v>6070.13</v>
+        <v>6980.96</v>
       </c>
     </row>
     <row r="392" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B392" s="4">
-        <v>34243</v>
+        <v>34425</v>
       </c>
       <c r="C392" s="7">
-        <v>4483.64</v>
+        <v>4641.04</v>
       </c>
       <c r="D392" s="8">
-        <v>5974.68</v>
+        <v>7046.25</v>
       </c>
     </row>
     <row r="393" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B393" s="4">
-        <v>34213</v>
+        <v>34394</v>
       </c>
       <c r="C393" s="5">
-        <v>4401.63</v>
+        <v>4598.19</v>
       </c>
       <c r="D393" s="6">
-        <v>6071.67</v>
+        <v>7062.58</v>
       </c>
     </row>
     <row r="394" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B394" s="4">
-        <v>34182</v>
+        <v>34366</v>
       </c>
       <c r="C394" s="7">
-        <v>4526.57</v>
+        <v>4606.21</v>
       </c>
       <c r="D394" s="8">
-        <v>6362.35</v>
+        <v>6839.5</v>
       </c>
     </row>
     <row r="395" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B395" s="4">
-        <v>34151</v>
+        <v>34335</v>
       </c>
       <c r="C395" s="5">
-        <v>4564.59</v>
+        <v>4659.04</v>
       </c>
       <c r="D395" s="6">
-        <v>6481.48</v>
+        <v>6746</v>
       </c>
     </row>
     <row r="396" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B396" s="4">
-        <v>34121</v>
+        <v>34304</v>
       </c>
       <c r="C396" s="7">
-        <v>4468.2</v>
+        <v>4637.46</v>
       </c>
       <c r="D396" s="8">
-        <v>6009.88</v>
+        <v>6562.65</v>
       </c>
     </row>
     <row r="397" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B397" s="4">
-        <v>34090</v>
+        <v>34274</v>
       </c>
       <c r="C397" s="5">
-        <v>4518.5</v>
+        <v>4587.09</v>
       </c>
       <c r="D397" s="6">
-        <v>6187.13</v>
+        <v>6070.13</v>
       </c>
     </row>
     <row r="398" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B398" s="4">
-        <v>34060</v>
+        <v>34243</v>
       </c>
       <c r="C398" s="7">
-        <v>4331.27</v>
+        <v>4483.64</v>
       </c>
       <c r="D398" s="8">
-        <v>5809.41</v>
+        <v>5974.68</v>
       </c>
     </row>
     <row r="399" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B399" s="4">
-        <v>34029</v>
+        <v>34213</v>
       </c>
       <c r="C399" s="5">
-        <v>4094.39</v>
+        <v>4401.63</v>
       </c>
       <c r="D399" s="6">
-        <v>5554.22</v>
+        <v>6071.67</v>
       </c>
     </row>
     <row r="400" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B400" s="4">
-        <v>34001</v>
+        <v>34182</v>
       </c>
       <c r="C400" s="7">
-        <v>4027.1</v>
+        <v>4526.57</v>
       </c>
       <c r="D400" s="8">
-        <v>6056.71</v>
+        <v>6362.35</v>
       </c>
     </row>
     <row r="401" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B401" s="4">
-        <v>33970</v>
+        <v>34151</v>
       </c>
       <c r="C401" s="5">
-        <v>3977.24</v>
+        <v>4564.59</v>
       </c>
       <c r="D401" s="6">
-        <v>6810.35</v>
+        <v>6481.48</v>
       </c>
     </row>
     <row r="402" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B402" s="4">
-        <v>33939</v>
+        <v>34121</v>
       </c>
       <c r="C402" s="7">
-        <v>3966.81</v>
+        <v>4468.2</v>
       </c>
       <c r="D402" s="8">
-        <v>6644.71</v>
+        <v>6009.88</v>
       </c>
     </row>
     <row r="403" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B403" s="4">
-        <v>33909</v>
+        <v>34090</v>
       </c>
       <c r="C403" s="5">
-        <v>3998.61</v>
+        <v>4518.5</v>
       </c>
       <c r="D403" s="6">
-        <v>6539.35</v>
+        <v>6187.13</v>
       </c>
     </row>
     <row r="404" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B404" s="4">
-        <v>33878</v>
+        <v>34060</v>
       </c>
       <c r="C404" s="7">
-        <v>4079</v>
+        <v>4331.27</v>
       </c>
       <c r="D404" s="8">
-        <v>7196.33</v>
+        <v>5809.41</v>
       </c>
     </row>
     <row r="405" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B405" s="4">
-        <v>33848</v>
+        <v>34029</v>
       </c>
       <c r="C405" s="5">
-        <v>4086.13</v>
+        <v>4094.39</v>
       </c>
       <c r="D405" s="6">
-        <v>7351.5</v>
+        <v>5554.22</v>
       </c>
     </row>
     <row r="406" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B406" s="4">
-        <v>33817</v>
+        <v>34001</v>
       </c>
       <c r="C406" s="7">
-        <v>4094</v>
+        <v>4027.1</v>
       </c>
       <c r="D406" s="8">
-        <v>7626.14</v>
+        <v>6056.71</v>
       </c>
     </row>
     <row r="407" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B407" s="4">
-        <v>33786</v>
+        <v>33970</v>
       </c>
       <c r="C407" s="5">
-        <v>4136.55</v>
+        <v>3977.24</v>
       </c>
       <c r="D407" s="6">
-        <v>7537</v>
+        <v>6810.35</v>
       </c>
     </row>
     <row r="408" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B408" s="4">
-        <v>33756</v>
+        <v>33939</v>
       </c>
       <c r="C408" s="7">
-        <v>4110.15</v>
+        <v>3966.81</v>
       </c>
       <c r="D408" s="8">
-        <v>7255.88</v>
+        <v>6644.71</v>
       </c>
     </row>
     <row r="409" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B409" s="4">
-        <v>33725</v>
+        <v>33909</v>
       </c>
       <c r="C409" s="5">
-        <v>4176.77</v>
+        <v>3998.61</v>
       </c>
       <c r="D409" s="6">
-        <v>7973.09</v>
+        <v>6539.35</v>
       </c>
     </row>
     <row r="410" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B410" s="4">
-        <v>33695</v>
+        <v>33878</v>
       </c>
       <c r="C410" s="7">
-        <v>4497.18</v>
+        <v>4079</v>
       </c>
       <c r="D410" s="8">
-        <v>8395.41</v>
+        <v>7196.33</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B411" s="4">
-        <v>33664</v>
+        <v>33848</v>
       </c>
       <c r="C411" s="5">
-        <v>4247.79</v>
+        <v>4086.13</v>
       </c>
       <c r="D411" s="6">
-        <v>7948.92</v>
+        <v>7351.5</v>
       </c>
     </row>
     <row r="412" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B412" s="4">
-        <v>33635</v>
+        <v>33817</v>
       </c>
       <c r="C412" s="7">
-        <v>4737.79</v>
+        <v>4094</v>
       </c>
       <c r="D412" s="8">
-        <v>8137.38</v>
+        <v>7626.14</v>
       </c>
     </row>
     <row r="413" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B413" s="4">
-        <v>33604</v>
+        <v>33786</v>
       </c>
       <c r="C413" s="5">
-        <v>4930.84</v>
+        <v>4136.55</v>
       </c>
       <c r="D413" s="6">
-        <v>8357.96</v>
+        <v>7537</v>
       </c>
     </row>
     <row r="414" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B414" s="4">
-        <v>33573</v>
+        <v>33756</v>
       </c>
       <c r="C414" s="7">
-        <v>4883.2</v>
+        <v>4110.15</v>
       </c>
       <c r="D414" s="8">
-        <v>7692.2</v>
+        <v>7255.88</v>
       </c>
     </row>
     <row r="415" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B415" s="4">
-        <v>33543</v>
+        <v>33725</v>
       </c>
       <c r="C415" s="5">
-        <v>4713.55</v>
+        <v>4176.77</v>
       </c>
       <c r="D415" s="6">
-        <v>7277.5</v>
+        <v>7973.09</v>
       </c>
     </row>
     <row r="416" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B416" s="4">
-        <v>33512</v>
+        <v>33695</v>
       </c>
       <c r="C416" s="7">
-        <v>4491.28</v>
+        <v>4497.18</v>
       </c>
       <c r="D416" s="8">
-        <v>7235.12</v>
+        <v>8395.41</v>
       </c>
     </row>
     <row r="417" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B417" s="4">
-        <v>33482</v>
+        <v>33664</v>
       </c>
       <c r="C417" s="5">
-        <v>4246.48</v>
+        <v>4247.79</v>
       </c>
       <c r="D417" s="6">
-        <v>6996.86</v>
+        <v>7948.92</v>
       </c>
     </row>
     <row r="418" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B418" s="4">
-        <v>33451</v>
+        <v>33635</v>
       </c>
       <c r="C418" s="7">
-        <v>4187.08</v>
+        <v>4737.79</v>
       </c>
       <c r="D418" s="8">
-        <v>6867.88</v>
+        <v>8137.38</v>
       </c>
     </row>
     <row r="419" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B419" s="4">
-        <v>33420</v>
+        <v>33604</v>
       </c>
       <c r="C419" s="5">
-        <v>4065.54</v>
+        <v>4930.84</v>
       </c>
       <c r="D419" s="6">
-        <v>7018.15</v>
+        <v>8357.96</v>
       </c>
     </row>
     <row r="420" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B420" s="4">
-        <v>33390</v>
+        <v>33573</v>
       </c>
       <c r="C420" s="7">
-        <v>3733.87</v>
+        <v>4883.2</v>
       </c>
       <c r="D420" s="8">
-        <v>6837</v>
+        <v>7692.2</v>
       </c>
     </row>
     <row r="421" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B421" s="4">
-        <v>33359</v>
+        <v>33543</v>
       </c>
       <c r="C421" s="5">
-        <v>3750.77</v>
+        <v>4713.55</v>
       </c>
       <c r="D421" s="6">
-        <v>6909.68</v>
+        <v>7277.5</v>
       </c>
     </row>
     <row r="422" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B422" s="4">
-        <v>33329</v>
+        <v>33512</v>
       </c>
       <c r="C422" s="7">
-        <v>3583.35</v>
+        <v>4491.28</v>
       </c>
       <c r="D422" s="8">
-        <v>6710.31</v>
+        <v>7235.12</v>
       </c>
     </row>
     <row r="423" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B423" s="4">
-        <v>33298</v>
+        <v>33482</v>
       </c>
       <c r="C423" s="5">
-        <v>3520.7</v>
+        <v>4246.48</v>
       </c>
       <c r="D423" s="6">
-        <v>6754.22</v>
+        <v>6996.86</v>
       </c>
     </row>
     <row r="424" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B424" s="4">
-        <v>33270</v>
+        <v>33451</v>
       </c>
       <c r="C424" s="7">
-        <v>3534.78</v>
+        <v>4187.08</v>
       </c>
       <c r="D424" s="8">
-        <v>6809.22</v>
+        <v>6867.88</v>
       </c>
     </row>
     <row r="425" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B425" s="4">
-        <v>33239</v>
+        <v>33420</v>
       </c>
       <c r="C425" s="5">
-        <v>3687.52</v>
+        <v>4065.54</v>
       </c>
       <c r="D425" s="6">
-        <v>6805.22</v>
+        <v>7018.15</v>
       </c>
     </row>
     <row r="426" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B426" s="4">
-        <v>33208</v>
+        <v>33390</v>
       </c>
       <c r="C426" s="7">
-        <v>3453.2</v>
+        <v>3733.87</v>
       </c>
       <c r="D426" s="8">
-        <v>6391.84</v>
+        <v>6837</v>
       </c>
     </row>
     <row r="427" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B427" s="4">
-        <v>33178</v>
+        <v>33359</v>
       </c>
       <c r="C427" s="5">
-        <v>3460.52</v>
+        <v>3750.77</v>
       </c>
       <c r="D427" s="6">
-        <v>6646.4</v>
+        <v>6909.68</v>
       </c>
     </row>
     <row r="428" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B428" s="4">
-        <v>33147</v>
+        <v>33329</v>
       </c>
       <c r="C428" s="7">
-        <v>3490.76</v>
+        <v>3583.35</v>
       </c>
       <c r="D428" s="8">
-        <v>6959.24</v>
+        <v>6710.31</v>
       </c>
     </row>
     <row r="429" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B429" s="4">
-        <v>33117</v>
+        <v>33298</v>
       </c>
       <c r="C429" s="5">
-        <v>3409.05</v>
+        <v>3520.7</v>
       </c>
       <c r="D429" s="6">
-        <v>6833.32</v>
+        <v>6754.22</v>
       </c>
     </row>
     <row r="430" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B430" s="4">
-        <v>33086</v>
+        <v>33270</v>
       </c>
       <c r="C430" s="7">
-        <v>3414.71</v>
+        <v>3534.78</v>
       </c>
       <c r="D430" s="8">
-        <v>6939.38</v>
+        <v>6809.22</v>
       </c>
     </row>
     <row r="431" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B431" s="4">
-        <v>33055</v>
+        <v>33239</v>
       </c>
       <c r="C431" s="5">
-        <v>3284.8</v>
+        <v>3687.52</v>
       </c>
       <c r="D431" s="6">
-        <v>6803.64</v>
+        <v>6805.22</v>
       </c>
     </row>
     <row r="432" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B432" s="4">
-        <v>33025</v>
+        <v>33208</v>
       </c>
       <c r="C432" s="7">
-        <v>3314.35</v>
+        <v>3453.2</v>
       </c>
       <c r="D432" s="8">
-        <v>6696.77</v>
+        <v>6391.84</v>
       </c>
     </row>
     <row r="433" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B433" s="4">
+        <v>33178</v>
+      </c>
+      <c r="C433" s="5">
+        <v>3460.52</v>
+      </c>
+      <c r="D433" s="6">
+        <v>6646.4</v>
+      </c>
+    </row>
+    <row r="434" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B434" s="4">
+        <v>33147</v>
+      </c>
+      <c r="C434" s="7">
+        <v>3490.76</v>
+      </c>
+      <c r="D434" s="8">
+        <v>6959.24</v>
+      </c>
+    </row>
+    <row r="435" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B435" s="4">
+        <v>33117</v>
+      </c>
+      <c r="C435" s="5">
+        <v>3409.05</v>
+      </c>
+      <c r="D435" s="6">
+        <v>6833.32</v>
+      </c>
+    </row>
+    <row r="436" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B436" s="4">
+        <v>33086</v>
+      </c>
+      <c r="C436" s="7">
+        <v>3414.71</v>
+      </c>
+      <c r="D436" s="8">
+        <v>6939.38</v>
+      </c>
+    </row>
+    <row r="437" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B437" s="4">
+        <v>33055</v>
+      </c>
+      <c r="C437" s="5">
+        <v>3284.8</v>
+      </c>
+      <c r="D437" s="6">
+        <v>6803.64</v>
+      </c>
+    </row>
+    <row r="438" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B438" s="4">
+        <v>33025</v>
+      </c>
+      <c r="C438" s="7">
+        <v>3314.35</v>
+      </c>
+      <c r="D438" s="8">
+        <v>6696.77</v>
+      </c>
+    </row>
+    <row r="439" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B439" s="4">
         <v>32994</v>
       </c>
-      <c r="C433" s="5">
+      <c r="C439" s="5">
         <v>3431.4</v>
       </c>
-      <c r="D433" s="6">
+      <c r="D439" s="6">
         <v>6734.4</v>
       </c>
     </row>
-    <row r="434" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B434" s="9">
+    <row r="440" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B440" s="9">
         <v>32964</v>
       </c>
-      <c r="C434" s="10">
+      <c r="C440" s="10">
         <v>3416.5</v>
       </c>
-      <c r="D434" s="11">
+      <c r="D440" s="11">
         <v>6755.8</v>
       </c>
     </row>
-    <row r="435" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="436" s="1" customFormat="1" ht="19.1988" customHeight="1">
-      <c r="B436" s="12" t="s">
+    <row r="441" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="442" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B442" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C436" s="12"/>
-      <c r="D436" s="12"/>
-      <c r="E436" s="12"/>
-    </row>
+      <c r="C442" s="12"/>
+      <c r="D442" s="12"/>
+      <c r="E442" s="12"/>
+    </row>
+    <row r="443" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B436:E436"/>
+    <mergeCell ref="B442:E442"/>
   </mergeCells>
   <pageSetup paperSize="8" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
